--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/6_five_bus_radial_grid_1ph_dd_MP_pf_sc_results_4_branch.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/6_five_bus_radial_grid_1ph_dd_MP_pf_sc_results_4_branch.xlsx
@@ -646,10 +646,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.8010071194443302</v>
+        <v>0.8010071194438338</v>
       </c>
       <c r="C2">
-        <v>0.8010071194443302</v>
+        <v>0.8010071194438338</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -658,40 +658,40 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>27.74770056203944</v>
+        <v>27.74770056202225</v>
       </c>
       <c r="G2">
-        <v>27.74770056203944</v>
+        <v>27.74770056202225</v>
       </c>
       <c r="H2">
-        <v>3.346522574510914</v>
+        <v>3.346522574404278</v>
       </c>
       <c r="I2">
-        <v>-2.345607201434881</v>
+        <v>-2.345607201329461</v>
       </c>
       <c r="J2">
-        <v>24.47415207743943</v>
+        <v>24.47415207745156</v>
       </c>
       <c r="K2">
-        <v>-23.33849811299676</v>
+        <v>-23.33849811301025</v>
       </c>
       <c r="L2">
-        <v>67.00637072519021</v>
+        <v>-82.99362927492926</v>
       </c>
       <c r="M2">
-        <v>-112.9936292748025</v>
+        <v>97.00637072506345</v>
       </c>
       <c r="N2">
-        <v>0.8902319386642066</v>
+        <v>0.8902319386646703</v>
       </c>
       <c r="O2">
-        <v>0.84533394365662</v>
+        <v>0.8453339436572478</v>
       </c>
       <c r="P2">
-        <v>149.220203107533</v>
+        <v>-0.7797968923376516</v>
       </c>
       <c r="Q2">
-        <v>151.2672005251284</v>
+        <v>1.267200525268436</v>
       </c>
     </row>
   </sheetData>
@@ -840,130 +840,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.4040872827794839</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4040872827794844</v>
+        <v>0.6998997044665642</v>
       </c>
       <c r="D2">
-        <v>0.8081745655589676</v>
+        <v>0.6998997044665651</v>
       </c>
       <c r="E2">
-        <v>0.4040872827794838</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.4040872827794842</v>
+        <v>0.699899704466564</v>
       </c>
       <c r="G2">
-        <v>0.8081745655589676</v>
+        <v>0.6998997044665649</v>
       </c>
       <c r="H2">
-        <v>4.66599802977679</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>4.665998029776795</v>
+        <v>8.081745655590209</v>
       </c>
       <c r="J2">
-        <v>9.331996059553576</v>
+        <v>8.081745655590218</v>
       </c>
       <c r="K2">
-        <v>4.665998029776788</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>4.665998029776793</v>
+        <v>8.081745655590206</v>
       </c>
       <c r="M2">
-        <v>9.331996059553576</v>
+        <v>8.081745655590217</v>
       </c>
       <c r="N2">
-        <v>-4.118843806451824</v>
+        <v>4.717044658585072E-30</v>
       </c>
       <c r="O2">
-        <v>4.705574455990267</v>
+        <v>5.292305105525001</v>
       </c>
       <c r="P2">
-        <v>1.17346129907689</v>
+        <v>-3.532113156927256</v>
       </c>
       <c r="Q2">
-        <v>4.203752804897837</v>
+        <v>-3.907985131378818E-15</v>
       </c>
       <c r="R2">
-        <v>-4.620665457544256</v>
+        <v>-5.037578110186938</v>
       </c>
       <c r="S2">
-        <v>-0.8338253052928438</v>
+        <v>3.786840152265324</v>
       </c>
       <c r="T2">
-        <v>2.709045627030869</v>
+        <v>-2.605323420919208E-15</v>
       </c>
       <c r="U2">
-        <v>1.631860734172156</v>
+        <v>5.972767095388922</v>
       </c>
       <c r="V2">
-        <v>8.681812722406109</v>
+        <v>7.049951988237542</v>
       </c>
       <c r="W2">
-        <v>-2.612706572505487</v>
+        <v>2.605323420919202E-15</v>
       </c>
       <c r="X2">
-        <v>-1.535521679646773</v>
+        <v>-5.683749931812739</v>
       </c>
       <c r="Y2">
-        <v>-8.296456504304585</v>
+        <v>-6.760934824661359</v>
       </c>
       <c r="Z2">
-        <v>6.959587487086181</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>6.959587487086217</v>
+        <v>-173.040412512906</v>
       </c>
       <c r="AB2">
-        <v>-173.0404125129065</v>
+        <v>6.959587487086696</v>
       </c>
       <c r="AC2">
-        <v>-173.0404125129065</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>-173.0404125129065</v>
+        <v>6.959587487086691</v>
       </c>
       <c r="AE2">
-        <v>6.959587487086227</v>
+        <v>-173.040412512906</v>
       </c>
       <c r="AF2">
-        <v>1.056556102276588</v>
+        <v>1.100000023840441</v>
       </c>
       <c r="AG2">
-        <v>1.067403370676885</v>
+        <v>0.9874262523505261</v>
       </c>
       <c r="AH2">
-        <v>0.9387871689794298</v>
+        <v>0.975690240474352</v>
       </c>
       <c r="AI2">
-        <v>1.060763956347575</v>
+        <v>1.100000023840441</v>
       </c>
       <c r="AJ2">
-        <v>1.043533397670165</v>
+        <v>0.9397573997051056</v>
       </c>
       <c r="AK2">
-        <v>0.8935122209227271</v>
+        <v>0.9588546236704317</v>
       </c>
       <c r="AL2">
-        <v>153.6258711927874</v>
+        <v>1.037363532456506E-13</v>
       </c>
       <c r="AM2">
-        <v>26.08578027740591</v>
+        <v>-124.583684958317</v>
       </c>
       <c r="AN2">
-        <v>-90.73804150814225</v>
+        <v>123.5710235121547</v>
       </c>
       <c r="AO2">
-        <v>155.097906710443</v>
+        <v>9.980330250131611E-14</v>
       </c>
       <c r="AP2">
-        <v>25.3420671882443</v>
+        <v>-124.5913819789044</v>
       </c>
       <c r="AQ2">
-        <v>-88.77958335489548</v>
+        <v>126.2130370003926</v>
       </c>
     </row>
   </sheetData>
@@ -1112,130 +1112,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0006849323693034941</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0006849323693034948</v>
+        <v>0.001186337663417456</v>
       </c>
       <c r="D2">
-        <v>0.00136986473860699</v>
+        <v>0.001186337663417455</v>
       </c>
       <c r="E2">
-        <v>0.0006849323693034939</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.0006849323693034947</v>
+        <v>0.001186337663417456</v>
       </c>
       <c r="G2">
-        <v>0.00136986473860699</v>
+        <v>0.001186337663417456</v>
       </c>
       <c r="H2">
-        <v>0.00790891775588121</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.007908917755881218</v>
+        <v>0.01369864738647719</v>
       </c>
       <c r="J2">
-        <v>0.01581783551176244</v>
+        <v>0.01369864738647718</v>
       </c>
       <c r="K2">
-        <v>0.007908917755881208</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>0.007908917755881217</v>
+        <v>0.01369864738647719</v>
       </c>
       <c r="M2">
-        <v>0.01581783551176244</v>
+        <v>0.01369864738647719</v>
       </c>
       <c r="N2">
-        <v>-0.002157821179101904</v>
+        <v>4.857225512153554E-18</v>
       </c>
       <c r="O2">
-        <v>0.008023606650512003</v>
+        <v>0.01388939212222374</v>
       </c>
       <c r="P2">
-        <v>0.01173157094282022</v>
+        <v>0.003707964292004403</v>
       </c>
       <c r="Q2">
-        <v>0.002158065127929206</v>
+        <v>-7.285838268230331E-18</v>
       </c>
       <c r="R2">
-        <v>-0.008023362701684699</v>
+        <v>-0.01388866027574178</v>
       </c>
       <c r="S2">
-        <v>-0.01173059514751101</v>
+        <v>-0.003707232445522455</v>
       </c>
       <c r="T2">
-        <v>0.008018048855952732</v>
+        <v>-4.857225512153554E-18</v>
       </c>
       <c r="U2">
-        <v>-0.002141964684332144</v>
+        <v>0.003734119487813197</v>
       </c>
       <c r="V2">
-        <v>0.0117521683432412</v>
+        <v>0.01389413302809683</v>
       </c>
       <c r="W2">
-        <v>-0.008017772067864243</v>
+        <v>7.285838268230331E-18</v>
       </c>
       <c r="X2">
-        <v>0.002142241472420635</v>
+        <v>-0.003733289123547691</v>
       </c>
       <c r="Y2">
-        <v>-0.01175106119088726</v>
+        <v>-0.01389330266383133</v>
       </c>
       <c r="Z2">
-        <v>44.93968234972677</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>44.93968234972684</v>
+        <v>-135.0603176519728</v>
       </c>
       <c r="AB2">
-        <v>-135.0603176502659</v>
+        <v>44.93968234801986</v>
       </c>
       <c r="AC2">
-        <v>-135.0603176502659</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>-135.0603176502658</v>
+        <v>44.93968234801989</v>
       </c>
       <c r="AE2">
-        <v>44.93968234972686</v>
+        <v>-135.0603176519728</v>
       </c>
       <c r="AF2">
-        <v>1.049869387330143</v>
+        <v>1.049999952316282</v>
       </c>
       <c r="AG2">
-        <v>1.050029087220759</v>
+        <v>1.049927663576823</v>
       </c>
       <c r="AH2">
-        <v>1.049797089600023</v>
+        <v>1.049767948256754</v>
       </c>
       <c r="AI2">
-        <v>1.049843609258968</v>
+        <v>1.049999952316282</v>
       </c>
       <c r="AJ2">
-        <v>1.050008313510067</v>
+        <v>1.049860334070201</v>
       </c>
       <c r="AK2">
-        <v>1.049703970218137</v>
+        <v>1.049695606600142</v>
       </c>
       <c r="AL2">
-        <v>150.0022784719103</v>
+        <v>1.292875712777592E-16</v>
       </c>
       <c r="AM2">
-        <v>29.99269099044346</v>
+        <v>-120.0123410858219</v>
       </c>
       <c r="AN2">
-        <v>-90.01006399193572</v>
+        <v>119.997246556448</v>
       </c>
       <c r="AO2">
-        <v>150.0044003598861</v>
+        <v>1.279628776179796E-16</v>
       </c>
       <c r="AP2">
-        <v>29.99041181059057</v>
+        <v>-120.0147787920383</v>
       </c>
       <c r="AQ2">
-        <v>-90.01038004812548</v>
+        <v>119.9992109149273</v>
       </c>
     </row>
   </sheetData>
@@ -1384,130 +1384,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0007175117889064331</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0007175117889064341</v>
+        <v>0.001242766873415578</v>
       </c>
       <c r="D2">
-        <v>0.001435023577812869</v>
+        <v>0.001242766873415577</v>
       </c>
       <c r="E2">
-        <v>0.000717511788906433</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.0007175117889064339</v>
+        <v>0.001242766873415577</v>
       </c>
       <c r="G2">
-        <v>0.001435023577812868</v>
+        <v>0.001242766873415577</v>
       </c>
       <c r="H2">
-        <v>0.008285112489437182</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.008285112489437195</v>
+        <v>0.01435023577812867</v>
       </c>
       <c r="J2">
-        <v>0.0165702249788744</v>
+        <v>0.01435023577812866</v>
       </c>
       <c r="K2">
-        <v>0.008285112489437181</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>0.008285112489437191</v>
+        <v>0.01435023577812866</v>
       </c>
       <c r="M2">
-        <v>0.01657022497887439</v>
+        <v>0.01435023577812866</v>
       </c>
       <c r="N2">
-        <v>-0.00236846563439915</v>
+        <v>1.908195864933515E-17</v>
       </c>
       <c r="O2">
-        <v>0.008805604922132663</v>
+        <v>0.01524274420986618</v>
       </c>
       <c r="P2">
-        <v>0.01287427857546706</v>
+        <v>0.004068673653334379</v>
       </c>
       <c r="Q2">
-        <v>0.002368733342451622</v>
+        <v>-2.162621980257983E-17</v>
       </c>
       <c r="R2">
-        <v>-0.008805337214080182</v>
+        <v>-0.01524194108570873</v>
       </c>
       <c r="S2">
-        <v>-0.01287320774325713</v>
+        <v>-0.004067870529176946</v>
       </c>
       <c r="T2">
-        <v>0.008799310099561718</v>
+        <v>-1.526556691946812E-17</v>
       </c>
       <c r="U2">
-        <v>-0.002350334331244474</v>
+        <v>0.004098641437072777</v>
       </c>
       <c r="V2">
-        <v>0.0128979515366345</v>
+        <v>0.01524828586787897</v>
       </c>
       <c r="W2">
-        <v>-0.008799006353891215</v>
+        <v>1.017704461297874E-17</v>
       </c>
       <c r="X2">
-        <v>0.002350638076914975</v>
+        <v>-0.004097730200061275</v>
       </c>
       <c r="Y2">
-        <v>-0.01289673655395249</v>
+        <v>-0.01524737463086747</v>
       </c>
       <c r="Z2">
-        <v>44.93730822328369</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>44.93730822328371</v>
+        <v>-135.0626917767089</v>
       </c>
       <c r="AB2">
+        <v>44.93730822328384</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>44.93730822328377</v>
+      </c>
+      <c r="AE2">
         <v>-135.0626917767089</v>
       </c>
-      <c r="AC2">
-        <v>-135.062691776709</v>
-      </c>
-      <c r="AD2">
-        <v>-135.062691776709</v>
-      </c>
-      <c r="AE2">
-        <v>44.93730822328378</v>
-      </c>
       <c r="AF2">
-        <v>1.099863250228143</v>
+        <v>1.100000023841856</v>
       </c>
       <c r="AG2">
-        <v>1.100030538759423</v>
+        <v>1.099924286805662</v>
       </c>
       <c r="AH2">
-        <v>1.099787503773014</v>
+        <v>1.099756982111964</v>
       </c>
       <c r="AI2">
-        <v>1.099836247687822</v>
+        <v>1.100000023841856</v>
       </c>
       <c r="AJ2">
-        <v>1.100008775115285</v>
+        <v>1.099853752771306</v>
       </c>
       <c r="AK2">
-        <v>1.099689954833211</v>
+        <v>1.099681201022607</v>
       </c>
       <c r="AL2">
-        <v>150.002278651371</v>
+        <v>1.216458562721449E-16</v>
       </c>
       <c r="AM2">
-        <v>29.99269129588955</v>
+        <v>-120.0123402953706</v>
       </c>
       <c r="AN2">
-        <v>-90.01006302180257</v>
+        <v>119.9972472210366</v>
       </c>
       <c r="AO2">
-        <v>150.0044004898158</v>
+        <v>1.099465206954569E-16</v>
       </c>
       <c r="AP2">
-        <v>29.99041227879359</v>
+        <v>-120.0147777254426</v>
       </c>
       <c r="AQ2">
-        <v>-90.01037885124794</v>
+        <v>119.9992116433414</v>
       </c>
     </row>
   </sheetData>
@@ -1656,130 +1656,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.3444552674418439</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.3444552674418443</v>
+        <v>0.5966140241441685</v>
       </c>
       <c r="D2">
-        <v>0.6889105348836895</v>
+        <v>0.596614024144169</v>
       </c>
       <c r="E2">
-        <v>0.344455267441844</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.3444552674418445</v>
+        <v>0.5966140241441683</v>
       </c>
       <c r="G2">
-        <v>0.6889105348836895</v>
+        <v>0.5966140241441691</v>
       </c>
       <c r="H2">
-        <v>3.977426827626663</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>3.977426827626668</v>
+        <v>6.889105348838832</v>
       </c>
       <c r="J2">
-        <v>7.954853655253344</v>
+        <v>6.889105348838838</v>
       </c>
       <c r="K2">
-        <v>3.977426827626664</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>3.977426827626669</v>
+        <v>6.88910534883883</v>
       </c>
       <c r="M2">
-        <v>7.954853655253344</v>
+        <v>6.889105348838839</v>
       </c>
       <c r="N2">
-        <v>-2.964806489477418</v>
+        <v>-1.1250259841699E-15</v>
       </c>
       <c r="O2">
-        <v>3.505468152228915</v>
+        <v>4.046129814981897</v>
       </c>
       <c r="P2">
-        <v>1.081323325502993</v>
+        <v>-2.424144826722033</v>
       </c>
       <c r="Q2">
-        <v>3.083266084099929</v>
+        <v>-4.446351442012288E-30</v>
       </c>
       <c r="R2">
-        <v>-3.387008557606411</v>
+        <v>-3.690751031114177</v>
       </c>
       <c r="S2">
-        <v>-0.6074849470129551</v>
+        <v>2.779523610589765</v>
       </c>
       <c r="T2">
-        <v>2.073035540333735</v>
+        <v>-2.250051968339811E-15</v>
       </c>
       <c r="U2">
-        <v>1.089170877936053</v>
+        <v>4.251377296201728</v>
       </c>
       <c r="V2">
-        <v>6.324412836539644</v>
+        <v>5.235241958602574</v>
       </c>
       <c r="W2">
-        <v>-2.003032375461038</v>
+        <v>2.250051968339809E-15</v>
       </c>
       <c r="X2">
-        <v>-1.019167713063354</v>
+        <v>-4.041367801583512</v>
       </c>
       <c r="Y2">
-        <v>-6.044400177048851</v>
+        <v>-5.025232463984359</v>
       </c>
       <c r="Z2">
-        <v>8.6461167959771</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>8.646116795977173</v>
+        <v>-171.3538832040131</v>
       </c>
       <c r="AB2">
-        <v>-171.3538832040156</v>
+        <v>8.646116795979623</v>
       </c>
       <c r="AC2">
-        <v>-171.3538832040156</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>-171.3538832040155</v>
+        <v>8.646116795979607</v>
       </c>
       <c r="AE2">
-        <v>8.646116795977102</v>
+        <v>-171.3538832040131</v>
       </c>
       <c r="AF2">
-        <v>0.9095509723192678</v>
+        <v>0.9499999880793201</v>
       </c>
       <c r="AG2">
-        <v>0.9229023352363644</v>
+        <v>0.8519274953374951</v>
       </c>
       <c r="AH2">
-        <v>0.8065751367405924</v>
+        <v>0.8374453463803448</v>
       </c>
       <c r="AI2">
-        <v>0.9244102655074492</v>
+        <v>0.9499999880793201</v>
       </c>
       <c r="AJ2">
-        <v>0.8892741171286339</v>
+        <v>0.794450310001205</v>
       </c>
       <c r="AK2">
-        <v>0.7636659326470617</v>
+        <v>0.83359293341623</v>
       </c>
       <c r="AL2">
-        <v>153.6843149089777</v>
+        <v>1.125719000044093E-13</v>
       </c>
       <c r="AM2">
-        <v>25.90646319985125</v>
+        <v>-124.9369013740785</v>
       </c>
       <c r="AN2">
-        <v>-91.05627425265098</v>
+        <v>123.4923063547485</v>
       </c>
       <c r="AO2">
-        <v>155.6364983178173</v>
+        <v>1.132227946037944E-13</v>
       </c>
       <c r="AP2">
-        <v>25.39291893522362</v>
+        <v>-123.7575561724106</v>
       </c>
       <c r="AQ2">
-        <v>-87.0930524816231</v>
+        <v>127.5936877880397</v>
       </c>
     </row>
   </sheetData>
@@ -1928,130 +1928,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.326326038289806</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.3263260382898062</v>
+        <v>0.5652132781507708</v>
       </c>
       <c r="D2">
-        <v>0.6526520765796132</v>
+        <v>0.5652132781507709</v>
       </c>
       <c r="E2">
-        <v>0.3263260382898059</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.3263260382898062</v>
+        <v>0.5652132781507706</v>
       </c>
       <c r="G2">
-        <v>0.6526520765796133</v>
+        <v>0.5652132781507712</v>
       </c>
       <c r="H2">
-        <v>3.768088521004072</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>3.768088521004074</v>
+        <v>6.526520765797968</v>
       </c>
       <c r="J2">
-        <v>7.536177042008159</v>
+        <v>6.526520765797969</v>
       </c>
       <c r="K2">
-        <v>3.768088521004071</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>3.768088521004074</v>
+        <v>6.526520765797965</v>
       </c>
       <c r="M2">
-        <v>7.536177042008161</v>
+        <v>6.526520765797971</v>
       </c>
       <c r="N2">
-        <v>-2.660934282006157</v>
+        <v>-1.065814075405996E-15</v>
       </c>
       <c r="O2">
-        <v>3.146181854988731</v>
+        <v>3.631429427972639</v>
       </c>
       <c r="P2">
-        <v>0.9704951459651533</v>
+        <v>-2.175686709020092</v>
       </c>
       <c r="Q2">
-        <v>2.767252585572454</v>
+        <v>1.065814075405997E-15</v>
       </c>
       <c r="R2">
-        <v>-3.039863551422437</v>
+        <v>-3.312474517273579</v>
       </c>
       <c r="S2">
-        <v>-0.5452219316999656</v>
+        <v>2.494641619719162</v>
       </c>
       <c r="T2">
-        <v>1.860563701769113</v>
+        <v>-1.065814075406E-15</v>
       </c>
       <c r="U2">
-        <v>0.977538378423351</v>
+        <v>3.815640458612123</v>
       </c>
       <c r="V2">
-        <v>5.676204160384986</v>
+        <v>4.698665781960718</v>
       </c>
       <c r="W2">
-        <v>-1.797735378261389</v>
+        <v>5.329070377030012E-16</v>
       </c>
       <c r="X2">
-        <v>-0.9147100549156255</v>
+        <v>-3.627155488088837</v>
       </c>
       <c r="Y2">
-        <v>-5.424890866354084</v>
+        <v>-4.510180811437437</v>
       </c>
       <c r="Z2">
-        <v>8.646116795977113</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>8.64611679597717</v>
+        <v>-171.3538832040131</v>
       </c>
       <c r="AB2">
-        <v>-171.3538832040156</v>
+        <v>8.646116795979593</v>
       </c>
       <c r="AC2">
-        <v>-171.3538832040156</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>-171.3538832040155</v>
+        <v>8.646116795979623</v>
       </c>
       <c r="AE2">
-        <v>8.646116795977122</v>
+        <v>-171.3538832040131</v>
       </c>
       <c r="AF2">
-        <v>0.8616798564989268</v>
+        <v>0.899999976158378</v>
       </c>
       <c r="AG2">
-        <v>0.8743285159282419</v>
+        <v>0.8070891948562782</v>
       </c>
       <c r="AH2">
-        <v>0.7641238031003671</v>
+        <v>0.7933692644565852</v>
       </c>
       <c r="AI2">
-        <v>0.875757081428299</v>
+        <v>0.899999976158378</v>
       </c>
       <c r="AJ2">
-        <v>0.8424702044808954</v>
+        <v>0.7526371252968913</v>
       </c>
       <c r="AK2">
-        <v>0.7234729787364325</v>
+        <v>0.7897196101204147</v>
       </c>
       <c r="AL2">
-        <v>153.6843149089777</v>
+        <v>1.125022285811001E-13</v>
       </c>
       <c r="AM2">
-        <v>25.90646319985125</v>
+        <v>-124.9369013740785</v>
       </c>
       <c r="AN2">
-        <v>-91.05627425265098</v>
+        <v>123.4923063547485</v>
       </c>
       <c r="AO2">
-        <v>155.6364983178173</v>
+        <v>1.135321887420955E-13</v>
       </c>
       <c r="AP2">
-        <v>25.39291893522362</v>
+        <v>-123.7575561724106</v>
       </c>
       <c r="AQ2">
-        <v>-87.0930524816231</v>
+        <v>127.5936877880397</v>
       </c>
     </row>
   </sheetData>
@@ -2200,130 +2200,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0006196380394649922</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0006196380394649938</v>
+        <v>0.001073244566655738</v>
       </c>
       <c r="D2">
-        <v>0.001239276078929988</v>
+        <v>0.001073244566655739</v>
       </c>
       <c r="E2">
-        <v>0.0006196380394649923</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.0006196380394649938</v>
+        <v>0.001073244566655738</v>
       </c>
       <c r="G2">
-        <v>0.001239276078929987</v>
+        <v>0.001073244566655739</v>
       </c>
       <c r="H2">
-        <v>0.007154963777704904</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.007154963777704923</v>
+        <v>0.01239276078929988</v>
       </c>
       <c r="J2">
-        <v>0.01430992755540985</v>
+        <v>0.01239276078929989</v>
       </c>
       <c r="K2">
-        <v>0.007154963777704906</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>0.007154963777704923</v>
+        <v>0.01239276078929988</v>
       </c>
       <c r="M2">
-        <v>0.01430992755540984</v>
+        <v>0.01239276078929989</v>
       </c>
       <c r="N2">
-        <v>-0.001766293229061209</v>
+        <v>-1.098658187665638E-18</v>
       </c>
       <c r="O2">
-        <v>0.006567433922238286</v>
+        <v>0.01136857461541536</v>
       </c>
       <c r="P2">
-        <v>0.009602281386354133</v>
+        <v>0.003034847464115875</v>
       </c>
       <c r="Q2">
-        <v>0.001766676566046989</v>
+        <v>5.493290938328191E-19</v>
       </c>
       <c r="R2">
-        <v>-0.006567050585252502</v>
+        <v>-0.01136742460445802</v>
       </c>
       <c r="S2">
-        <v>-0.009600748038411005</v>
+        <v>-0.003033697453158531</v>
       </c>
       <c r="T2">
-        <v>0.006562798547193103</v>
+        <v>-2.197316375331276E-18</v>
       </c>
       <c r="U2">
-        <v>-0.001753174490991384</v>
+        <v>0.003056449565210324</v>
       </c>
       <c r="V2">
-        <v>0.009619248112403484</v>
+        <v>0.01137242260339486</v>
       </c>
       <c r="W2">
-        <v>-0.006562572015924761</v>
+        <v>1.098658187665638E-18</v>
       </c>
       <c r="X2">
-        <v>0.00175340102225973</v>
+        <v>-0.003055769971405284</v>
       </c>
       <c r="Y2">
-        <v>-0.009618341987330106</v>
+        <v>-0.01137174300958982</v>
       </c>
       <c r="Z2">
-        <v>44.93890368274601</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>44.93890368274601</v>
+        <v>-135.0610963172468</v>
       </c>
       <c r="AB2">
+        <v>44.93890368274593</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>44.938903682746</v>
+      </c>
+      <c r="AE2">
         <v>-135.0610963172468</v>
       </c>
-      <c r="AC2">
-        <v>-135.0610963172467</v>
-      </c>
-      <c r="AD2">
-        <v>-135.0610963172467</v>
-      </c>
-      <c r="AE2">
-        <v>44.93890368274594</v>
-      </c>
       <c r="AF2">
-        <v>0.949876382337129</v>
+        <v>0.9499999880790745</v>
       </c>
       <c r="AG2">
-        <v>0.9500274430299663</v>
+        <v>0.9499312985903232</v>
       </c>
       <c r="AH2">
-        <v>0.9498076839092892</v>
+        <v>0.9497802226059002</v>
       </c>
       <c r="AI2">
-        <v>0.9498597353478825</v>
+        <v>0.9499999880790745</v>
       </c>
       <c r="AJ2">
-        <v>0.9499838462230685</v>
+        <v>0.9498274465944925</v>
       </c>
       <c r="AK2">
-        <v>0.9496871683818422</v>
+        <v>0.9497033152804026</v>
       </c>
       <c r="AL2">
-        <v>150.0023929725076</v>
+        <v>1.601848169756723E-16</v>
       </c>
       <c r="AM2">
-        <v>29.99234777609229</v>
+        <v>-120.0129131626927</v>
       </c>
       <c r="AN2">
-        <v>-90.01052169766018</v>
+        <v>119.9971322138703</v>
       </c>
       <c r="AO2">
-        <v>150.0060099968999</v>
+        <v>1.644574311781012E-16</v>
       </c>
       <c r="AP2">
-        <v>29.98966943394204</v>
+        <v>-120.0146543330408</v>
       </c>
       <c r="AQ2">
-        <v>-90.00864540853816</v>
+        <v>120.0016883560018</v>
       </c>
     </row>
   </sheetData>
@@ -2472,130 +2472,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0005870255028874318</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0005870255028874333</v>
+        <v>0.001016757996339705</v>
       </c>
       <c r="D2">
-        <v>0.001174051005774866</v>
+        <v>0.001016757996339705</v>
       </c>
       <c r="E2">
-        <v>0.0005870255028874317</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.0005870255028874334</v>
+        <v>0.001016757996339705</v>
       </c>
       <c r="G2">
-        <v>0.001174051005774866</v>
+        <v>0.001016757996339705</v>
       </c>
       <c r="H2">
-        <v>0.006778386642264684</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.006778386642264701</v>
+        <v>0.01174051005774867</v>
       </c>
       <c r="J2">
-        <v>0.01355677328452939</v>
+        <v>0.01174051005774867</v>
       </c>
       <c r="K2">
-        <v>0.006778386642264683</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>0.006778386642264703</v>
+        <v>0.01174051005774867</v>
       </c>
       <c r="M2">
-        <v>0.01355677328452939</v>
+        <v>0.01174051005774867</v>
       </c>
       <c r="N2">
-        <v>-0.001585260360824677</v>
+        <v>1.561251087020101E-18</v>
       </c>
       <c r="O2">
-        <v>0.005894317261688895</v>
+        <v>0.0102033741625531</v>
       </c>
       <c r="P2">
-        <v>0.008618113801728406</v>
+        <v>0.002723796540039549</v>
       </c>
       <c r="Q2">
-        <v>0.001585604408414511</v>
+        <v>-1.561251087020101E-18</v>
       </c>
       <c r="R2">
-        <v>-0.005893973214099063</v>
+        <v>-0.01020234201978361</v>
       </c>
       <c r="S2">
-        <v>-0.008616737611369073</v>
+        <v>-0.002722764397270047</v>
       </c>
       <c r="T2">
-        <v>0.005890156980600921</v>
+        <v>1.040834058013401E-18</v>
       </c>
       <c r="U2">
-        <v>-0.001573486202885348</v>
+        <v>0.002743184574830209</v>
       </c>
       <c r="V2">
-        <v>0.008633341555431176</v>
+        <v>0.01020682775831651</v>
       </c>
       <c r="W2">
-        <v>-0.005889953667224473</v>
+        <v>-1.040834058013401E-18</v>
       </c>
       <c r="X2">
-        <v>0.001573689516261794</v>
+        <v>-0.002742574634700867</v>
       </c>
       <c r="Y2">
-        <v>-0.008632528301925393</v>
+        <v>-0.01020621781818717</v>
       </c>
       <c r="Z2">
-        <v>44.93890368274603</v>
+        <v>0</v>
       </c>
       <c r="AA2">
+        <v>-135.0610963172467</v>
+      </c>
+      <c r="AB2">
+        <v>44.93890368274597</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
         <v>44.93890368274599</v>
       </c>
-      <c r="AB2">
+      <c r="AE2">
         <v>-135.0610963172468</v>
       </c>
-      <c r="AC2">
-        <v>-135.0610963172467</v>
-      </c>
-      <c r="AD2">
-        <v>-135.0610963172467</v>
-      </c>
-      <c r="AE2">
-        <v>44.93890368274594</v>
-      </c>
       <c r="AF2">
-        <v>0.8998828759831982</v>
+        <v>0.8999999761581453</v>
       </c>
       <c r="AG2">
-        <v>0.9000259861112592</v>
+        <v>0.8999349019065515</v>
       </c>
       <c r="AH2">
-        <v>0.8998177932629938</v>
+        <v>0.8997917772917252</v>
       </c>
       <c r="AI2">
-        <v>0.8998671051515003</v>
+        <v>0.8999999761581453</v>
       </c>
       <c r="AJ2">
-        <v>0.8999846838737214</v>
+        <v>0.8998365158066097</v>
       </c>
       <c r="AK2">
-        <v>0.8997036206596359</v>
+        <v>0.8997189177212169</v>
       </c>
       <c r="AL2">
-        <v>150.0023929725076</v>
+        <v>1.578038501752602E-16</v>
       </c>
       <c r="AM2">
-        <v>29.99234777609228</v>
+        <v>-120.0129131626927</v>
       </c>
       <c r="AN2">
-        <v>-90.0105216976602</v>
+        <v>119.9971322138703</v>
       </c>
       <c r="AO2">
-        <v>150.0060099968999</v>
+        <v>1.630704362421682E-16</v>
       </c>
       <c r="AP2">
-        <v>29.98966943394203</v>
+        <v>-120.0146543330408</v>
       </c>
       <c r="AQ2">
-        <v>-90.00864540853816</v>
+        <v>120.0016883560018</v>
       </c>
     </row>
   </sheetData>
@@ -2783,40 +2783,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>2.122312365535515E-08</v>
+        <v>2.82974980587398E-08</v>
       </c>
       <c r="O2">
-        <v>2.122312207120572E-08</v>
+        <v>7.074374916407734E-09</v>
       </c>
       <c r="P2">
-        <v>-1.107708409339612E-19</v>
+        <v>7.074375760584905E-09</v>
       </c>
       <c r="Q2">
-        <v>-2.122312365311296E-08</v>
+        <v>-2.829749805548971E-08</v>
       </c>
       <c r="R2">
-        <v>-2.122312206908824E-08</v>
+        <v>-7.074374915784353E-09</v>
       </c>
       <c r="S2">
-        <v>2.302004043792982E-24</v>
+        <v>-7.074375760209499E-09</v>
       </c>
       <c r="T2">
-        <v>-1.225317517435747E-08</v>
+        <v>1.012360369055781E-17</v>
       </c>
       <c r="U2">
-        <v>1.225317622221384E-08</v>
+        <v>1.225317512957492E-08</v>
       </c>
       <c r="V2">
-        <v>-4.191313195388274E-16</v>
+        <v>-1.225317482713396E-08</v>
       </c>
       <c r="W2">
-        <v>1.225317517682783E-08</v>
+        <v>-6.766547267488993E-18</v>
       </c>
       <c r="X2">
-        <v>-1.225317621993535E-08</v>
+        <v>-1.22531751292046E-08</v>
       </c>
       <c r="Y2">
-        <v>4.19203319730506E-16</v>
+        <v>1.225317482822742E-08</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2837,40 +2837,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>1.049999952501994</v>
+        <v>1.049999952294509</v>
       </c>
       <c r="AH2">
-        <v>1.049999952097912</v>
+        <v>1.049999952108799</v>
       </c>
       <c r="AI2">
-        <v>1.049999952316284</v>
+        <v>1.049999952512881</v>
       </c>
       <c r="AJ2">
-        <v>1.049999952474803</v>
+        <v>1.049999952189404</v>
       </c>
       <c r="AK2">
-        <v>1.049999951967445</v>
+        <v>1.049999952030885</v>
       </c>
       <c r="AL2">
-        <v>1.049999952316284</v>
+        <v>1.049999952538243</v>
       </c>
       <c r="AM2">
-        <v>149.9999999803838</v>
+        <v>-2.546078072533754E-08</v>
       </c>
       <c r="AN2">
-        <v>29.99999998141774</v>
+        <v>-120.0000000058458</v>
       </c>
       <c r="AO2">
-        <v>-89.99999999999632</v>
+        <v>119.9999999931154</v>
       </c>
       <c r="AP2">
-        <v>149.9999999730199</v>
+        <v>-3.196814954853224E-08</v>
       </c>
       <c r="AQ2">
-        <v>29.99999997902068</v>
+        <v>-120.0000000049892</v>
       </c>
       <c r="AR2">
-        <v>-89.99999999999632</v>
+        <v>119.9999999890051</v>
       </c>
     </row>
   </sheetData>
@@ -3058,40 +3058,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>2.329250078385902E-08</v>
+        <v>3.105666841677214E-08</v>
       </c>
       <c r="O2">
-        <v>2.32925023681922E-08</v>
+        <v>7.764163352778654E-09</v>
       </c>
       <c r="P2">
-        <v>1.791981398729517E-15</v>
+        <v>7.764165670130243E-09</v>
       </c>
       <c r="Q2">
-        <v>-2.329250078167241E-08</v>
+        <v>-3.105666841349552E-08</v>
       </c>
       <c r="R2">
-        <v>-2.329250236544038E-08</v>
+        <v>-7.764163352324802E-09</v>
       </c>
       <c r="S2">
-        <v>-1.792256666446049E-15</v>
+        <v>-7.764165669197563E-09</v>
       </c>
       <c r="T2">
-        <v>-1.34479310658379E-08</v>
+        <v>1.802933837888605E-15</v>
       </c>
       <c r="U2">
-        <v>1.344792942246099E-08</v>
+        <v>1.344793438869622E-08</v>
       </c>
       <c r="V2">
-        <v>7.277779473312372E-16</v>
+        <v>-1.344793292502877E-08</v>
       </c>
       <c r="W2">
-        <v>1.34479310688849E-08</v>
+        <v>-1.799683008618316E-15</v>
       </c>
       <c r="X2">
-        <v>-1.344792941989075E-08</v>
+        <v>-1.344793438782155E-08</v>
       </c>
       <c r="Y2">
-        <v>-7.281042715778386E-16</v>
+        <v>1.344793292619417E-08</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -3112,40 +3112,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>1.100000024036411</v>
+        <v>1.100000023819046</v>
       </c>
       <c r="AH2">
-        <v>1.100000023613087</v>
+        <v>1.100000023624493</v>
       </c>
       <c r="AI2">
-        <v>1.100000023841858</v>
+        <v>1.100000024047816</v>
       </c>
       <c r="AJ2">
-        <v>1.100000024007926</v>
+        <v>1.100000023708936</v>
       </c>
       <c r="AK2">
-        <v>1.100000023476407</v>
+        <v>1.100000023542868</v>
       </c>
       <c r="AL2">
-        <v>1.100000023841858</v>
+        <v>1.100000024074386</v>
       </c>
       <c r="AM2">
-        <v>149.9999999803838</v>
+        <v>-2.546078078319625E-08</v>
       </c>
       <c r="AN2">
-        <v>29.99999998141774</v>
+        <v>-120.0000000058458</v>
       </c>
       <c r="AO2">
-        <v>-89.99999999999632</v>
+        <v>119.9999999931154</v>
       </c>
       <c r="AP2">
-        <v>149.9999999730199</v>
+        <v>-3.1968149034895E-08</v>
       </c>
       <c r="AQ2">
-        <v>29.99999997902068</v>
+        <v>-120.0000000049892</v>
       </c>
       <c r="AR2">
-        <v>-89.99999999999632</v>
+        <v>119.9999999890051</v>
       </c>
     </row>
   </sheetData>
@@ -3333,40 +3333,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>2.122309127911833E-08</v>
+        <v>2.829739592246483E-08</v>
       </c>
       <c r="O2">
-        <v>2.122300124299808E-08</v>
+        <v>7.074305156353634E-09</v>
       </c>
       <c r="P2">
-        <v>-1.111512571297674E-19</v>
+        <v>7.074394452494937E-09</v>
       </c>
       <c r="Q2">
-        <v>-2.122309127687617E-08</v>
+        <v>-2.829739591921476E-08</v>
       </c>
       <c r="R2">
-        <v>-2.122300124088063E-08</v>
+        <v>-7.074305155730255E-09</v>
       </c>
       <c r="S2">
-        <v>3.835575445017843E-22</v>
+        <v>-7.074394452119536E-09</v>
       </c>
       <c r="T2">
-        <v>-1.225305434639676E-08</v>
+        <v>1.021456641885976E-13</v>
       </c>
       <c r="U2">
-        <v>1.22532085975456E-08</v>
+        <v>1.225315643715774E-08</v>
       </c>
       <c r="V2">
-        <v>-4.191434308906495E-16</v>
+        <v>-1.225310506694019E-08</v>
       </c>
       <c r="W2">
-        <v>1.225305434886706E-08</v>
+        <v>-1.021423071356878E-13</v>
       </c>
       <c r="X2">
-        <v>-1.225320859526712E-08</v>
+        <v>-1.225315643678743E-08</v>
       </c>
       <c r="Y2">
-        <v>4.192154331562285E-16</v>
+        <v>1.225310506803363E-08</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -3387,40 +3387,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>1.049999952501991</v>
+        <v>1.049999952294507</v>
       </c>
       <c r="AH2">
-        <v>1.049999952097912</v>
+        <v>1.0499999521088</v>
       </c>
       <c r="AI2">
-        <v>1.049999952316284</v>
+        <v>1.04999995251288</v>
       </c>
       <c r="AJ2">
-        <v>1.049999952474801</v>
+        <v>1.049999952189402</v>
       </c>
       <c r="AK2">
-        <v>1.049999951967445</v>
+        <v>1.049999952030886</v>
       </c>
       <c r="AL2">
-        <v>1.049999952316284</v>
+        <v>1.049999952538242</v>
       </c>
       <c r="AM2">
-        <v>149.9999999803839</v>
+        <v>-2.546068453912746E-08</v>
       </c>
       <c r="AN2">
-        <v>29.99999998141785</v>
+        <v>-120.0000000058458</v>
       </c>
       <c r="AO2">
-        <v>-89.99999999999632</v>
+        <v>119.9999999931154</v>
       </c>
       <c r="AP2">
-        <v>149.9999999730199</v>
+        <v>-3.196800917406381E-08</v>
       </c>
       <c r="AQ2">
-        <v>29.99999997902082</v>
+        <v>-120.0000000049891</v>
       </c>
       <c r="AR2">
-        <v>-89.99999999999632</v>
+        <v>119.9999999890051</v>
       </c>
     </row>
   </sheetData>
@@ -3491,10 +3491,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.8081745664560928</v>
+        <v>0.8081745664566463</v>
       </c>
       <c r="C2">
-        <v>0.8081745664560928</v>
+        <v>0.8081745664566463</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -3503,40 +3503,40 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>27.99598820973805</v>
+        <v>27.99598820975723</v>
       </c>
       <c r="G2">
-        <v>27.99598820973805</v>
+        <v>27.99598820975723</v>
       </c>
       <c r="H2">
-        <v>3.520383623374711</v>
+        <v>3.520383623275721</v>
       </c>
       <c r="I2">
-        <v>-2.501475639760505</v>
+        <v>-2.501475639660094</v>
       </c>
       <c r="J2">
-        <v>26.0454382249792</v>
+        <v>26.04543822501815</v>
       </c>
       <c r="K2">
-        <v>-24.88936956810797</v>
+        <v>-24.8893695681453</v>
       </c>
       <c r="L2">
-        <v>66.95958696689573</v>
+        <v>-83.04041303320911</v>
       </c>
       <c r="M2">
-        <v>-113.040413033097</v>
+        <v>96.9595869667836</v>
       </c>
       <c r="N2">
-        <v>0.9387871686716606</v>
+        <v>0.9387871686719225</v>
       </c>
       <c r="O2">
-        <v>0.8935122209062166</v>
+        <v>0.8935122209065726</v>
       </c>
       <c r="P2">
-        <v>149.2619585801569</v>
+        <v>-0.7380414197227492</v>
       </c>
       <c r="Q2">
-        <v>151.2204167668212</v>
+        <v>1.22041676695381</v>
       </c>
     </row>
   </sheetData>
@@ -3724,40 +3724,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>2.329246525077523E-08</v>
+        <v>3.105655632160062E-08</v>
       </c>
       <c r="O2">
-        <v>2.329236975855427E-08</v>
+        <v>7.764086790723125E-09</v>
       </c>
       <c r="P2">
-        <v>1.791979578083485E-15</v>
+        <v>7.764186184617179E-09</v>
       </c>
       <c r="Q2">
-        <v>-2.329246524858864E-08</v>
+        <v>-3.105655631832401E-08</v>
       </c>
       <c r="R2">
-        <v>-2.329236975580247E-08</v>
+        <v>-7.764086790269269E-09</v>
       </c>
       <c r="S2">
-        <v>-1.792254845736831E-15</v>
+        <v>-7.764186183684505E-09</v>
       </c>
       <c r="T2">
-        <v>-1.344779845644766E-08</v>
+        <v>1.138972711655645E-13</v>
       </c>
       <c r="U2">
-        <v>1.344796495461025E-08</v>
+        <v>1.34479138736391E-08</v>
       </c>
       <c r="V2">
-        <v>7.277785504117614E-16</v>
+        <v>-1.34478563628003E-08</v>
       </c>
       <c r="W2">
-        <v>1.344779845949463E-08</v>
+        <v>-1.138940203690357E-13</v>
       </c>
       <c r="X2">
-        <v>-1.344796495204003E-08</v>
+        <v>-1.344791387276443E-08</v>
       </c>
       <c r="Y2">
-        <v>-7.28104879142778E-16</v>
+        <v>1.34478563639657E-08</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -3778,40 +3778,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>1.100000024036409</v>
+        <v>1.100000023819044</v>
       </c>
       <c r="AH2">
-        <v>1.100000023613086</v>
+        <v>1.100000023624493</v>
       </c>
       <c r="AI2">
-        <v>1.100000023841858</v>
+        <v>1.100000024047815</v>
       </c>
       <c r="AJ2">
-        <v>1.100000024007923</v>
+        <v>1.100000023708934</v>
       </c>
       <c r="AK2">
-        <v>1.100000023476407</v>
+        <v>1.100000023542869</v>
       </c>
       <c r="AL2">
-        <v>1.100000023841858</v>
+        <v>1.100000024074385</v>
       </c>
       <c r="AM2">
-        <v>149.9999999803839</v>
+        <v>-2.546068459697317E-08</v>
       </c>
       <c r="AN2">
-        <v>29.99999998141785</v>
+        <v>-120.0000000058457</v>
       </c>
       <c r="AO2">
-        <v>-89.99999999999632</v>
+        <v>119.9999999931154</v>
       </c>
       <c r="AP2">
-        <v>149.9999999730199</v>
+        <v>-3.196800866041471E-08</v>
       </c>
       <c r="AQ2">
-        <v>29.99999997902082</v>
+        <v>-120.0000000049891</v>
       </c>
       <c r="AR2">
-        <v>-89.99999999999632</v>
+        <v>119.9999999890051</v>
       </c>
     </row>
   </sheetData>
@@ -3999,40 +3999,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.737312409248506E-08</v>
+        <v>2.316416632889467E-08</v>
       </c>
       <c r="O2">
-        <v>1.737312591264991E-08</v>
+        <v>5.791042880983848E-09</v>
       </c>
       <c r="P2">
-        <v>5.64538444096456E-16</v>
+        <v>5.79104088980678E-09</v>
       </c>
       <c r="Q2">
-        <v>-1.737312408897552E-08</v>
+        <v>-2.316416632429741E-08</v>
       </c>
       <c r="R2">
-        <v>-1.737312590996274E-08</v>
+        <v>-5.791042879604986E-09</v>
       </c>
       <c r="S2">
-        <v>-5.640572064271834E-16</v>
+        <v>-5.79104088910494E-09</v>
       </c>
       <c r="T2">
-        <v>-1.003037981512091E-08</v>
+        <v>-2.247461720119847E-15</v>
       </c>
       <c r="U2">
-        <v>1.003037763154779E-08</v>
+        <v>1.003037713022923E-08</v>
       </c>
       <c r="V2">
-        <v>-7.003235696170272E-17</v>
+        <v>-1.003037811992335E-08</v>
       </c>
       <c r="W2">
-        <v>1.00303798164399E-08</v>
+        <v>2.250483475867914E-15</v>
       </c>
       <c r="X2">
-        <v>-1.003037762939527E-08</v>
+        <v>-1.003037712989277E-08</v>
       </c>
       <c r="Y2">
-        <v>7.050715121414172E-17</v>
+        <v>1.003037812051145E-08</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -4053,40 +4053,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.9499999882545976</v>
+        <v>0.9499999880579761</v>
       </c>
       <c r="AH2">
-        <v>0.9499999878719021</v>
+        <v>0.9499999878824495</v>
       </c>
       <c r="AI2">
-        <v>0.949999988079071</v>
+        <v>0.949999988265145</v>
       </c>
       <c r="AJ2">
-        <v>0.9499999881643812</v>
+        <v>0.9499999878753937</v>
       </c>
       <c r="AK2">
-        <v>0.9499999876882448</v>
+        <v>0.9499999877900835</v>
       </c>
       <c r="AL2">
-        <v>0.949999988079071</v>
+        <v>0.9499999882662198</v>
       </c>
       <c r="AM2">
-        <v>149.9999999794544</v>
+        <v>-2.665150595126174E-08</v>
       </c>
       <c r="AN2">
-        <v>29.9999999805611</v>
+        <v>-120.0000000061071</v>
       </c>
       <c r="AO2">
-        <v>-89.99999999999632</v>
+        <v>119.9999999927813</v>
       </c>
       <c r="AP2">
-        <v>149.9999999698057</v>
+        <v>-3.315887541540026E-08</v>
       </c>
       <c r="AQ2">
-        <v>29.99999998044882</v>
+        <v>-120.0000000029657</v>
       </c>
       <c r="AR2">
-        <v>-89.99999999999632</v>
+        <v>119.9999999863863</v>
       </c>
     </row>
   </sheetData>
@@ -4274,40 +4274,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.559249875069889E-08</v>
+        <v>2.07899991171137E-08</v>
       </c>
       <c r="O2">
-        <v>1.559250038430939E-08</v>
+        <v>5.197500944924649E-09</v>
       </c>
       <c r="P2">
-        <v>5.066771502325841E-16</v>
+        <v>5.197499157829492E-09</v>
       </c>
       <c r="Q2">
-        <v>-1.559249874754905E-08</v>
+        <v>-2.078999911298763E-08</v>
       </c>
       <c r="R2">
-        <v>-1.559250038189763E-08</v>
+        <v>-5.197500943687111E-09</v>
       </c>
       <c r="S2">
-        <v>-5.062452334891482E-16</v>
+        <v>-5.197499157199586E-09</v>
       </c>
       <c r="T2">
-        <v>-9.002335095503062E-09</v>
+        <v>-2.017112408686578E-15</v>
       </c>
       <c r="U2">
-        <v>9.002333135731114E-09</v>
+        <v>9.002332685794244E-09</v>
       </c>
       <c r="V2">
-        <v>-6.285451587346899E-17</v>
+        <v>-9.002333574051562E-09</v>
       </c>
       <c r="W2">
-        <v>9.00233509668686E-09</v>
+        <v>2.019824450467423E-15</v>
       </c>
       <c r="X2">
-        <v>-9.002333133799214E-09</v>
+        <v>-9.002332685492268E-09</v>
       </c>
       <c r="Y2">
-        <v>6.328064908356439E-17</v>
+        <v>9.002333574579384E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -4328,40 +4328,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.8999999763244304</v>
+        <v>0.8999999761381574</v>
       </c>
       <c r="AH2">
-        <v>0.8999999759618766</v>
+        <v>0.899999975971869</v>
       </c>
       <c r="AI2">
-        <v>0.899999976158142</v>
+        <v>0.8999999763344226</v>
       </c>
       <c r="AJ2">
-        <v>0.8999999762389622</v>
+        <v>0.8999999759651847</v>
       </c>
       <c r="AK2">
-        <v>0.8999999757878855</v>
+        <v>0.8999999758843643</v>
       </c>
       <c r="AL2">
-        <v>0.899999976158142</v>
+        <v>0.8999999763354409</v>
       </c>
       <c r="AM2">
-        <v>149.9999999794544</v>
+        <v>-2.665150595126173E-08</v>
       </c>
       <c r="AN2">
-        <v>29.99999998056109</v>
+        <v>-120.0000000061071</v>
       </c>
       <c r="AO2">
-        <v>-89.99999999999632</v>
+        <v>119.9999999927813</v>
       </c>
       <c r="AP2">
-        <v>149.9999999698057</v>
+        <v>-3.315887541540027E-08</v>
       </c>
       <c r="AQ2">
-        <v>29.99999998044881</v>
+        <v>-120.0000000029657</v>
       </c>
       <c r="AR2">
-        <v>-89.99999999999632</v>
+        <v>119.9999999863863</v>
       </c>
     </row>
   </sheetData>
@@ -4549,40 +4549,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.737309758950993E-08</v>
+        <v>2.316408272074315E-08</v>
       </c>
       <c r="O2">
-        <v>1.737302700339843E-08</v>
+        <v>5.790985775802734E-09</v>
       </c>
       <c r="P2">
-        <v>5.645346289227953E-16</v>
+        <v>5.791056190906701E-09</v>
       </c>
       <c r="Q2">
-        <v>-1.737309758600042E-08</v>
+        <v>-2.316408271614593E-08</v>
       </c>
       <c r="R2">
-        <v>-1.737302700071127E-08</v>
+        <v>-5.790985774423882E-09</v>
       </c>
       <c r="S2">
-        <v>-5.640533887405103E-16</v>
+        <v>-5.791056190204871E-09</v>
       </c>
       <c r="T2">
-        <v>-1.003028090604747E-08</v>
+        <v>8.136011018669638E-14</v>
       </c>
       <c r="U2">
-        <v>1.003040413383255E-08</v>
+        <v>1.003036182873111E-08</v>
       </c>
       <c r="V2">
-        <v>-7.003414120016934E-17</v>
+        <v>-1.003032101464457E-08</v>
       </c>
       <c r="W2">
-        <v>1.003028090736644E-08</v>
+        <v>-8.13570884562264E-14</v>
       </c>
       <c r="X2">
-        <v>-1.003040413168003E-08</v>
+        <v>-1.003036182839466E-08</v>
       </c>
       <c r="Y2">
-        <v>7.050892945992885E-17</v>
+        <v>1.003032101523267E-08</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -4603,40 +4603,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.9499999882545958</v>
+        <v>0.9499999880579746</v>
       </c>
       <c r="AH2">
-        <v>0.9499999878719017</v>
+        <v>0.9499999878824499</v>
       </c>
       <c r="AI2">
-        <v>0.949999988079071</v>
+        <v>0.9499999882651439</v>
       </c>
       <c r="AJ2">
-        <v>0.9499999881643791</v>
+        <v>0.9499999878753924</v>
       </c>
       <c r="AK2">
-        <v>0.949999987688245</v>
+        <v>0.9499999877900843</v>
       </c>
       <c r="AL2">
-        <v>0.949999988079071</v>
+        <v>0.9499999882662183</v>
       </c>
       <c r="AM2">
-        <v>149.9999999794545</v>
+        <v>-2.665140516394285E-08</v>
       </c>
       <c r="AN2">
-        <v>29.99999998056121</v>
+        <v>-120.0000000061071</v>
       </c>
       <c r="AO2">
-        <v>-89.99999999999632</v>
+        <v>119.9999999927813</v>
       </c>
       <c r="AP2">
-        <v>149.9999999698057</v>
+        <v>-3.315871139514769E-08</v>
       </c>
       <c r="AQ2">
-        <v>29.99999998044897</v>
+        <v>-120.0000000029656</v>
       </c>
       <c r="AR2">
-        <v>-89.99999999999632</v>
+        <v>119.9999999863863</v>
       </c>
     </row>
   </sheetData>
@@ -4824,40 +4824,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.559247496409582E-08</v>
+        <v>2.07899240782208E-08</v>
       </c>
       <c r="O2">
-        <v>1.55924116125737E-08</v>
+        <v>5.197449692630561E-09</v>
       </c>
       <c r="P2">
-        <v>5.066737270716422E-16</v>
+        <v>5.197512890672254E-09</v>
       </c>
       <c r="Q2">
-        <v>-1.559247496094601E-08</v>
+        <v>-2.078992407409477E-08</v>
       </c>
       <c r="R2">
-        <v>-1.559241161016196E-08</v>
+        <v>-5.197449691393032E-09</v>
       </c>
       <c r="S2">
-        <v>-5.062418099515709E-16</v>
+        <v>-5.197512890042353E-09</v>
       </c>
       <c r="T2">
-        <v>-9.002246323927163E-09</v>
+        <v>7.302126029391914E-14</v>
       </c>
       <c r="U2">
-        <v>9.002356921714565E-09</v>
+        <v>9.00231895259411E-09</v>
       </c>
       <c r="V2">
-        <v>-6.285612167303637E-17</v>
+        <v>-9.002282321669812E-09</v>
       </c>
       <c r="W2">
-        <v>9.002246325110956E-09</v>
+        <v>-7.301854827216117E-14</v>
       </c>
       <c r="X2">
-        <v>-9.002356919782669E-09</v>
+        <v>-9.002318952292142E-09</v>
       </c>
       <c r="Y2">
-        <v>6.328225128118609E-17</v>
+        <v>9.002282322197636E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -4878,40 +4878,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.8999999763244286</v>
+        <v>0.899999976138156</v>
       </c>
       <c r="AH2">
-        <v>0.8999999759618762</v>
+        <v>0.8999999759718693</v>
       </c>
       <c r="AI2">
-        <v>0.899999976158142</v>
+        <v>0.8999999763344215</v>
       </c>
       <c r="AJ2">
-        <v>0.8999999762389603</v>
+        <v>0.8999999759651834</v>
       </c>
       <c r="AK2">
-        <v>0.8999999757878858</v>
+        <v>0.8999999758843652</v>
       </c>
       <c r="AL2">
-        <v>0.899999976158142</v>
+        <v>0.8999999763354395</v>
       </c>
       <c r="AM2">
-        <v>149.9999999794545</v>
+        <v>-2.665140516394285E-08</v>
       </c>
       <c r="AN2">
-        <v>29.9999999805612</v>
+        <v>-120.0000000061071</v>
       </c>
       <c r="AO2">
-        <v>-89.99999999999632</v>
+        <v>119.9999999927813</v>
       </c>
       <c r="AP2">
-        <v>149.9999999698057</v>
+        <v>-3.315871139514769E-08</v>
       </c>
       <c r="AQ2">
-        <v>29.99999998044897</v>
+        <v>-120.0000000029656</v>
       </c>
       <c r="AR2">
-        <v>-89.99999999999632</v>
+        <v>119.9999999863863</v>
       </c>
     </row>
   </sheetData>
@@ -5063,130 +5063,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.4005035592935327</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4005035602966113</v>
+        <v>0.6936925142782041</v>
       </c>
       <c r="D2">
-        <v>0.8010071195901436</v>
+        <v>0.6936925136990756</v>
       </c>
       <c r="E2">
-        <v>0.4005035592935325</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.400503560296611</v>
+        <v>0.6936925142782037</v>
       </c>
       <c r="G2">
-        <v>0.8010071195901435</v>
+        <v>0.6936925136990757</v>
       </c>
       <c r="H2">
-        <v>4.624616755390488</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>4.624616766973041</v>
+        <v>8.01007119706699</v>
       </c>
       <c r="J2">
-        <v>9.249233522363523</v>
+        <v>8.01007119037979</v>
       </c>
       <c r="K2">
-        <v>4.624616755390485</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>4.624616766973038</v>
+        <v>8.010071197066985</v>
       </c>
       <c r="M2">
-        <v>9.249233522363523</v>
+        <v>8.01007119037979</v>
       </c>
       <c r="N2">
-        <v>-3.895007721414303</v>
+        <v>7.074378450361146E-09</v>
       </c>
       <c r="O2">
-        <v>4.452761487274405</v>
+        <v>5.010515252527373</v>
       </c>
       <c r="P2">
-        <v>1.115507510497082</v>
+        <v>-3.337253951625872</v>
       </c>
       <c r="Q2">
-        <v>3.978417335658773</v>
+        <v>-7.074380937083573E-09</v>
       </c>
       <c r="R2">
-        <v>-4.369351872612127</v>
+        <v>-4.760286409094437</v>
       </c>
       <c r="S2">
-        <v>-0.7818690526835907</v>
+        <v>3.587482794641007</v>
       </c>
       <c r="T2">
-        <v>2.552472351685454</v>
+        <v>-6.839759426124495E-15</v>
       </c>
       <c r="U2">
-        <v>1.526552996056291</v>
+        <v>5.605578331363087</v>
       </c>
       <c r="V2">
-        <v>8.158050695483556</v>
+        <v>6.631497705214777</v>
       </c>
       <c r="W2">
-        <v>-2.457834521517802</v>
+        <v>6.83996029464954E-15</v>
       </c>
       <c r="X2">
-        <v>-1.431915165414591</v>
+        <v>-5.321664840066428</v>
       </c>
       <c r="Y2">
-        <v>-7.779499373864851</v>
+        <v>-6.347584214392178</v>
       </c>
       <c r="Z2">
-        <v>7.006370647647809</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>7.006370630012102</v>
+        <v>-172.993629237046</v>
       </c>
       <c r="AB2">
-        <v>-172.9936293611628</v>
+        <v>7.006370768825235</v>
       </c>
       <c r="AC2">
-        <v>-172.9936293523449</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>-172.9936293699806</v>
+        <v>7.006370762946705</v>
       </c>
       <c r="AE2">
-        <v>7.006370638829966</v>
+        <v>-172.9936292311675</v>
       </c>
       <c r="AG2">
-        <v>1.006968728209203</v>
+        <v>1.049999952309436</v>
       </c>
       <c r="AH2">
-        <v>1.017850815416664</v>
+        <v>0.9386302707700944</v>
       </c>
       <c r="AI2">
-        <v>0.8902319386138721</v>
+        <v>0.9268184944823479</v>
       </c>
       <c r="AJ2">
-        <v>1.011198185272837</v>
+        <v>1.04999995228316</v>
       </c>
       <c r="AK2">
-        <v>0.9942448480817322</v>
+        <v>0.8913852178563029</v>
       </c>
       <c r="AL2">
-        <v>0.8453339436546886</v>
+        <v>0.9102563143092106</v>
       </c>
       <c r="AM2">
-        <v>153.7687858248206</v>
+        <v>-6.365088208563842E-09</v>
       </c>
       <c r="AN2">
-        <v>25.92977054381189</v>
+        <v>-124.7853905158022</v>
       </c>
       <c r="AO2">
-        <v>-90.77979687712462</v>
+        <v>123.7198713610588</v>
       </c>
       <c r="AP2">
-        <v>155.2989288432828</v>
+        <v>-7.991931999153676E-09</v>
       </c>
       <c r="AQ2">
-        <v>25.15127081747185</v>
+        <v>-124.8066037984886</v>
       </c>
       <c r="AR2">
-        <v>-88.73279945368191</v>
+        <v>126.4803292547915</v>
       </c>
     </row>
   </sheetData>
@@ -5338,130 +5338,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.4040872825683051</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4040872836192547</v>
+        <v>0.699899705339962</v>
       </c>
       <c r="D2">
-        <v>0.8081745661875596</v>
+        <v>0.6998997047331965</v>
       </c>
       <c r="E2">
-        <v>0.4040872825683048</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.4040872836192543</v>
+        <v>0.6998997053399622</v>
       </c>
       <c r="G2">
-        <v>0.8081745661875593</v>
+        <v>0.6998997047331965</v>
       </c>
       <c r="H2">
-        <v>4.665998027338307</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>4.665998039473627</v>
+        <v>8.081745665675337</v>
       </c>
       <c r="J2">
-        <v>9.331996066811932</v>
+        <v>8.081745658669012</v>
       </c>
       <c r="K2">
-        <v>4.665998027338302</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>4.665998039473623</v>
+        <v>8.081745665675339</v>
       </c>
       <c r="M2">
-        <v>9.331996066811929</v>
+        <v>8.081745658669012</v>
       </c>
       <c r="N2">
-        <v>-4.118843823462727</v>
+        <v>7.764168617139235E-09</v>
       </c>
       <c r="O2">
-        <v>4.70557445261476</v>
+        <v>5.292305064293616</v>
       </c>
       <c r="P2">
-        <v>1.173461235011572</v>
+        <v>-3.532113212440751</v>
       </c>
       <c r="Q2">
-        <v>4.20375282181999</v>
+        <v>-7.764171222268358E-09</v>
       </c>
       <c r="R2">
-        <v>-4.620665453815831</v>
+        <v>-5.037578068319811</v>
       </c>
       <c r="S2">
-        <v>-0.8338252406991931</v>
+        <v>3.786840207972903</v>
       </c>
       <c r="T2">
-        <v>2.709045600331777</v>
+        <v>-4.560178521865181E-15</v>
       </c>
       <c r="U2">
-        <v>1.631860767623762</v>
+        <v>5.972767137375438</v>
       </c>
       <c r="V2">
-        <v>8.681812735911141</v>
+        <v>7.04995196746301</v>
       </c>
       <c r="W2">
-        <v>-2.612706545907089</v>
+        <v>5.211729831622965E-15</v>
       </c>
       <c r="X2">
-        <v>-1.535521712697959</v>
+        <v>-5.683749973077934</v>
       </c>
       <c r="Y2">
-        <v>-8.296456517210162</v>
+        <v>-6.760934803666622</v>
       </c>
       <c r="Z2">
-        <v>6.959587131118231</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>6.959587112928221</v>
+        <v>-173.0404128982055</v>
       </c>
       <c r="AB2">
-        <v>-173.0404128779694</v>
+        <v>6.95958710785056</v>
       </c>
       <c r="AC2">
-        <v>-173.0404128688745</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>-173.0404128870645</v>
+        <v>6.959587101787226</v>
       </c>
       <c r="AE2">
-        <v>6.959587122023284</v>
+        <v>-173.0404128921422</v>
       </c>
       <c r="AG2">
-        <v>1.056556102730337</v>
+        <v>1.100000023834738</v>
       </c>
       <c r="AH2">
-        <v>1.067403370124121</v>
+        <v>0.9874262516232873</v>
       </c>
       <c r="AI2">
-        <v>0.9387871687638322</v>
+        <v>0.9756902408813</v>
       </c>
       <c r="AJ2">
-        <v>1.06076395697307</v>
+        <v>1.100000023807211</v>
       </c>
       <c r="AK2">
-        <v>1.043533396977033</v>
+        <v>0.9397573989174056</v>
       </c>
       <c r="AL2">
-        <v>0.8935122209115925</v>
+        <v>0.9588546244070927</v>
       </c>
       <c r="AM2">
-        <v>153.6258712047109</v>
+        <v>-6.365089898714063E-09</v>
       </c>
       <c r="AN2">
-        <v>26.08578027955623</v>
+        <v>-124.5836849221281</v>
       </c>
       <c r="AO2">
-        <v>-90.73804144616004</v>
+        <v>123.5710235611746</v>
       </c>
       <c r="AP2">
-        <v>155.0979067193904</v>
+        <v>-7.991935153539628E-09</v>
       </c>
       <c r="AQ2">
-        <v>25.34206719699512</v>
+        <v>-124.5913819213517</v>
       </c>
       <c r="AR2">
-        <v>-88.77958326946406</v>
+        <v>126.2130370563715</v>
       </c>
     </row>
   </sheetData>
@@ -5613,130 +5613,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0003426969056497967</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0003426976206432038</v>
+        <v>0.0005935692777895701</v>
       </c>
       <c r="D2">
-        <v>0.0006853945262926165</v>
+        <v>0.000593568864987825</v>
       </c>
       <c r="E2">
-        <v>0.0003426969056497967</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.0003426976206432038</v>
+        <v>0.0005935692777895697</v>
       </c>
       <c r="G2">
-        <v>0.000685394526292616</v>
+        <v>0.0005935688649878246</v>
       </c>
       <c r="H2">
-        <v>0.003957123014547238</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.003957131270579959</v>
+        <v>0.006853947646290001</v>
       </c>
       <c r="J2">
-        <v>0.007914254285122763</v>
+        <v>0.006853942879666028</v>
       </c>
       <c r="K2">
-        <v>0.003957123014547238</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>0.003957131270579959</v>
+        <v>0.006853947646289996</v>
       </c>
       <c r="M2">
-        <v>0.007914254285122758</v>
+        <v>0.006853942879666023</v>
       </c>
       <c r="N2">
-        <v>-0.001077509975952131</v>
+        <v>7.074361217541638E-09</v>
       </c>
       <c r="O2">
-        <v>0.004013964220128088</v>
+        <v>0.006950404315618606</v>
       </c>
       <c r="P2">
-        <v>0.005872887265265731</v>
+        <v>0.001858930119459655</v>
       </c>
       <c r="Q2">
-        <v>0.001077571045361343</v>
+        <v>-7.074361219186062E-09</v>
       </c>
       <c r="R2">
-        <v>-0.004013903150464047</v>
+        <v>-0.006950221106881306</v>
       </c>
       <c r="S2">
-        <v>-0.005872642987119214</v>
+        <v>-0.001858746910977181</v>
       </c>
       <c r="T2">
-        <v>0.004012564526713235</v>
+        <v>1.231713798393069E-14</v>
       </c>
       <c r="U2">
-        <v>-0.001073542741585355</v>
+        <v>0.001865479043580662</v>
       </c>
       <c r="V2">
-        <v>0.005878043570213405</v>
+        <v>0.006951586311878806</v>
       </c>
       <c r="W2">
-        <v>-0.004012495236423022</v>
+        <v>-1.231936572944417E-14</v>
       </c>
       <c r="X2">
-        <v>0.001073612032164704</v>
+        <v>-0.001865271172131753</v>
       </c>
       <c r="Y2">
-        <v>-0.005877766408474289</v>
+        <v>-0.006951378440719027</v>
       </c>
       <c r="Z2">
-        <v>44.96988051999517</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>44.96976110516922</v>
+        <v>-135.0301990903664</v>
       </c>
       <c r="AB2">
-        <v>-135.0301791874718</v>
+        <v>44.96984071455453</v>
       </c>
       <c r="AC2">
-        <v>-135.0301194799975</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>-135.0302388948234</v>
+        <v>44.96980090962636</v>
       </c>
       <c r="AE2">
-        <v>44.96982081252092</v>
+        <v>-135.0301592854382</v>
       </c>
       <c r="AG2">
-        <v>1.049934614633216</v>
+        <v>1.049999952310839</v>
       </c>
       <c r="AH2">
-        <v>1.050014562658118</v>
+        <v>1.049963836942829</v>
       </c>
       <c r="AI2">
-        <v>1.049898497017663</v>
+        <v>1.049883885055195</v>
       </c>
       <c r="AJ2">
-        <v>1.049921706095978</v>
+        <v>1.049999952284563</v>
       </c>
       <c r="AK2">
-        <v>1.05000417821581</v>
+        <v>1.049930158571339</v>
       </c>
       <c r="AL2">
-        <v>1.049851907180982</v>
+        <v>1.0498476806368</v>
       </c>
       <c r="AM2">
-        <v>150.0011380535502</v>
+        <v>-6.365182841518859E-09</v>
       </c>
       <c r="AN2">
-        <v>29.9963433929199</v>
+        <v>-120.0061755328619</v>
       </c>
       <c r="AO2">
-        <v>-90.00503781811663</v>
+        <v>119.9986191676098</v>
       </c>
       <c r="AP2">
-        <v>150.0021992481837</v>
+        <v>-7.992019132460424E-09</v>
       </c>
       <c r="AQ2">
-        <v>29.99520276689581</v>
+        <v>-120.007395896147</v>
       </c>
       <c r="AR2">
-        <v>-90.00519704499436</v>
+        <v>119.9996008742948</v>
       </c>
     </row>
   </sheetData>
@@ -5888,130 +5888,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0003590067075384128</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0003590074565948201</v>
+        <v>0.0006218187226567905</v>
       </c>
       <c r="D2">
-        <v>0.0007180141641328762</v>
+        <v>0.0006218182901888928</v>
       </c>
       <c r="E2">
-        <v>0.0003590067075384124</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.00035900745659482</v>
+        <v>0.0006218187226567902</v>
       </c>
       <c r="G2">
-        <v>0.0007180141641328757</v>
+        <v>0.0006218182901888926</v>
       </c>
       <c r="H2">
-        <v>0.004145452384763678</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.004145461034122045</v>
+        <v>0.007180144138260946</v>
       </c>
       <c r="J2">
-        <v>0.008290913418881605</v>
+        <v>0.007180139144551801</v>
       </c>
       <c r="K2">
-        <v>0.004145452384763673</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>0.004145461034122043</v>
+        <v>0.007180144138260941</v>
       </c>
       <c r="M2">
-        <v>0.008290913418881598</v>
+        <v>0.0071801391445518</v>
       </c>
       <c r="N2">
-        <v>-0.001182634781699233</v>
+        <v>7.764152791844853E-09</v>
       </c>
       <c r="O2">
-        <v>0.004405261575625725</v>
+        <v>0.007627872841307269</v>
       </c>
       <c r="P2">
-        <v>0.006445230295394424</v>
+        <v>0.002039976483864464</v>
       </c>
       <c r="Q2">
-        <v>0.001182701802324966</v>
+        <v>-7.764152792922687E-09</v>
       </c>
       <c r="R2">
-        <v>-0.004405194554720316</v>
+        <v>-0.007627671778870717</v>
       </c>
       <c r="S2">
-        <v>-0.006444962212332143</v>
+        <v>-0.002039775421707587</v>
       </c>
       <c r="T2">
-        <v>0.004403676480401186</v>
+        <v>1.403328197511207E-14</v>
       </c>
       <c r="U2">
-        <v>-0.001178098065486511</v>
+        <v>0.002047480349500999</v>
       </c>
       <c r="V2">
-        <v>0.006451156829788092</v>
+        <v>0.007629254895391929</v>
       </c>
       <c r="W2">
-        <v>-0.004403600437769246</v>
+        <v>-1.403306152212075E-14</v>
       </c>
       <c r="X2">
-        <v>0.001178174108435769</v>
+        <v>-0.002047252220970543</v>
       </c>
       <c r="Y2">
-        <v>-0.006450852658625707</v>
+        <v>-0.007629026767178798</v>
       </c>
       <c r="Z2">
-        <v>44.96869186024399</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>44.96857244489649</v>
+        <v>-135.0313877506233</v>
       </c>
       <c r="AB2">
-        <v>-135.0313678474814</v>
+        <v>44.96865205448189</v>
       </c>
       <c r="AC2">
-        <v>-135.0313081397487</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>-135.0314275550962</v>
+        <v>44.96861224936941</v>
       </c>
       <c r="AE2">
-        <v>44.96863215251133</v>
+        <v>-135.0313479455108</v>
       </c>
       <c r="AG2">
-        <v>1.099931577028501</v>
+        <v>1.100000023836154</v>
       </c>
       <c r="AH2">
-        <v>1.100015328069929</v>
+        <v>1.099962187187774</v>
       </c>
       <c r="AI2">
-        <v>1.099893738025534</v>
+        <v>1.099878432099895</v>
       </c>
       <c r="AJ2">
-        <v>1.099918054564372</v>
+        <v>1.100000023808626</v>
       </c>
       <c r="AK2">
-        <v>1.100004448951734</v>
+        <v>1.09992690549233</v>
       </c>
       <c r="AL2">
-        <v>1.099844930798716</v>
+        <v>1.099840505013794</v>
       </c>
       <c r="AM2">
-        <v>150.0011380985991</v>
+        <v>-6.365182812305289E-09</v>
       </c>
       <c r="AN2">
-        <v>29.99634346929062</v>
+        <v>-120.0061753350593</v>
       </c>
       <c r="AO2">
-        <v>-90.00503757523745</v>
+        <v>119.998619334106</v>
       </c>
       <c r="AP2">
-        <v>150.0021992808796</v>
+        <v>-7.992019144778538E-09</v>
       </c>
       <c r="AQ2">
-        <v>29.99520288400391</v>
+        <v>-120.0073956292025</v>
       </c>
       <c r="AR2">
-        <v>-90.00519674530973</v>
+        <v>119.9996010568388</v>
       </c>
     </row>
   </sheetData>
@@ -6163,130 +6163,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.3444552665636509</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.3444552674676349</v>
+        <v>0.5966140256311127</v>
       </c>
       <c r="D2">
-        <v>0.688910534031287</v>
+        <v>0.5966140251091975</v>
       </c>
       <c r="E2">
-        <v>0.3444552665636509</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.3444552674676348</v>
+        <v>0.5966140256311125</v>
       </c>
       <c r="G2">
-        <v>0.6889105340312871</v>
+        <v>0.5966140251091976</v>
       </c>
       <c r="H2">
-        <v>3.977426817486164</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>3.977426827924471</v>
+        <v>6.889105366008583</v>
       </c>
       <c r="J2">
-        <v>7.954853645410648</v>
+        <v>6.889105359982027</v>
       </c>
       <c r="K2">
-        <v>3.977426817486163</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>3.977426827924469</v>
+        <v>6.889105366008582</v>
       </c>
       <c r="M2">
-        <v>7.954853645410649</v>
+        <v>6.889105359982028</v>
       </c>
       <c r="N2">
-        <v>-2.964806462211071</v>
+        <v>5.791043690345823E-09</v>
       </c>
       <c r="O2">
-        <v>3.50546816341167</v>
+        <v>4.04612975554782</v>
       </c>
       <c r="P2">
-        <v>1.081323385028083</v>
+        <v>-2.424144912675898</v>
       </c>
       <c r="Q2">
-        <v>3.083266056229552</v>
+        <v>-5.791043690067574E-09</v>
       </c>
       <c r="R2">
-        <v>-3.387008568771426</v>
+        <v>-3.690750969908676</v>
       </c>
       <c r="S2">
-        <v>-0.6074850077106222</v>
+        <v>2.779523697693283</v>
       </c>
       <c r="T2">
-        <v>2.073035560382315</v>
+        <v>-2.250725392642714E-15</v>
       </c>
       <c r="U2">
-        <v>1.089170850062064</v>
+        <v>4.25137736015934</v>
       </c>
       <c r="V2">
-        <v>6.324412820888821</v>
+        <v>5.235241933633194</v>
       </c>
       <c r="W2">
-        <v>-2.003032395866566</v>
+        <v>2.813402814062638E-15</v>
       </c>
       <c r="X2">
-        <v>-1.01916768517888</v>
+        <v>-4.041367864494309</v>
       </c>
       <c r="Y2">
-        <v>-6.044400162090959</v>
+        <v>-5.025232438335597</v>
       </c>
       <c r="Z2">
-        <v>8.646117273639709</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>8.646117250775164</v>
+        <v>-171.3538839821111</v>
       </c>
       <c r="AB2">
-        <v>-171.3538827377853</v>
+        <v>8.64611602550313</v>
       </c>
       <c r="AC2">
-        <v>-171.353882726353</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>-171.3538827492175</v>
+        <v>8.646116017881628</v>
       </c>
       <c r="AE2">
-        <v>8.646117262207417</v>
+        <v>-171.3538839744896</v>
       </c>
       <c r="AG2">
-        <v>0.9095509719084587</v>
+        <v>0.9499999880740464</v>
       </c>
       <c r="AH2">
-        <v>0.9229023357728192</v>
+        <v>0.8519274939915801</v>
       </c>
       <c r="AI2">
-        <v>0.8065751370603603</v>
+        <v>0.8374453469793219</v>
       </c>
       <c r="AJ2">
-        <v>0.9244102647831079</v>
+        <v>0.9499999880284007</v>
       </c>
       <c r="AK2">
-        <v>0.8892741177300129</v>
+        <v>0.7944503087731309</v>
       </c>
       <c r="AL2">
-        <v>0.7636659324840646</v>
+        <v>0.8335929349295949</v>
       </c>
       <c r="AM2">
-        <v>153.6843148789623</v>
+        <v>-6.662766360748564E-09</v>
       </c>
       <c r="AN2">
-        <v>25.90646318737687</v>
+        <v>-124.9369013014279</v>
       </c>
       <c r="AO2">
-        <v>-91.05627433392327</v>
+        <v>123.4923064630833</v>
       </c>
       <c r="AP2">
-        <v>155.6364982922236</v>
+        <v>-8.289608662391244E-09</v>
       </c>
       <c r="AQ2">
-        <v>25.39291890536854</v>
+        <v>-123.7575560332534</v>
       </c>
       <c r="AR2">
-        <v>-87.09305259910923</v>
+        <v>127.5936879018894</v>
       </c>
     </row>
   </sheetData>
@@ -6357,10 +6357,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0006853945262934878</v>
+        <v>0.0006853945262934886</v>
       </c>
       <c r="C2">
-        <v>0.0006853945262934878</v>
+        <v>0.0006853945262934886</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -6369,10 +6369,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.02374276285539847</v>
+        <v>0.0237427628553985</v>
       </c>
       <c r="G2">
-        <v>0.02374276285539847</v>
+        <v>0.0237427628553985</v>
       </c>
       <c r="H2">
         <v>0.01761866179579698</v>
@@ -6381,28 +6381,28 @@
         <v>-0.01761792896135745</v>
       </c>
       <c r="J2">
-        <v>0.01763413071068521</v>
+        <v>0.01763413071068529</v>
       </c>
       <c r="K2">
-        <v>-0.01763329922546786</v>
+        <v>-0.01763329922546793</v>
       </c>
       <c r="L2">
-        <v>104.9698208124451</v>
+        <v>-45.03017918754896</v>
       </c>
       <c r="M2">
-        <v>-75.03017918754762</v>
+        <v>134.9698208124438</v>
       </c>
       <c r="N2">
-        <v>1.049898497017662</v>
+        <v>1.049898497017663</v>
       </c>
       <c r="O2">
-        <v>1.049851907180982</v>
+        <v>1.049851907180983</v>
       </c>
       <c r="P2">
-        <v>149.9949621818736</v>
+        <v>-0.005037818120266383</v>
       </c>
       <c r="Q2">
-        <v>149.9948029549959</v>
+        <v>-0.005197044997986881</v>
       </c>
     </row>
   </sheetData>
@@ -6554,130 +6554,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.3263260374578336</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.3263260383142395</v>
+        <v>0.5652132795594546</v>
       </c>
       <c r="D2">
-        <v>0.6526520757720741</v>
+        <v>0.5652132790650085</v>
       </c>
       <c r="E2">
-        <v>0.3263260374578335</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.3263260383142394</v>
+        <v>0.5652132795594546</v>
       </c>
       <c r="G2">
-        <v>0.6526520757720743</v>
+        <v>0.5652132790650085</v>
       </c>
       <c r="H2">
-        <v>3.768088511397282</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>3.768088521286206</v>
+        <v>6.526520782064046</v>
       </c>
       <c r="J2">
-        <v>7.536177032683501</v>
+        <v>6.526520776354674</v>
       </c>
       <c r="K2">
-        <v>3.768088511397281</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>3.768088521286205</v>
+        <v>6.526520782064046</v>
       </c>
       <c r="M2">
-        <v>7.536177032683502</v>
+        <v>6.526520776354674</v>
       </c>
       <c r="N2">
-        <v>-2.66093425753442</v>
+        <v>5.197500958462644E-09</v>
       </c>
       <c r="O2">
-        <v>3.146181865025333</v>
+        <v>3.631429374630148</v>
       </c>
       <c r="P2">
-        <v>0.9704951993893268</v>
+        <v>-2.175686786164278</v>
       </c>
       <c r="Q2">
-        <v>2.767252560558598</v>
+        <v>-5.197501491119952E-09</v>
       </c>
       <c r="R2">
-        <v>-3.039863561443118</v>
+        <v>-3.312474462341219</v>
       </c>
       <c r="S2">
-        <v>-0.5452219861765386</v>
+        <v>2.494641697895173</v>
       </c>
       <c r="T2">
-        <v>1.860563719762852</v>
+        <v>-1.599325515974516E-15</v>
       </c>
       <c r="U2">
-        <v>0.9775383534062519</v>
+        <v>3.81564051601452</v>
       </c>
       <c r="V2">
-        <v>5.676204146338266</v>
+        <v>4.69866575955053</v>
       </c>
       <c r="W2">
-        <v>-1.797735396575487</v>
+        <v>2.132380130146873E-15</v>
       </c>
       <c r="X2">
-        <v>-0.9147100298891164</v>
+        <v>-3.627155544551712</v>
       </c>
       <c r="Y2">
-        <v>-5.424890852929273</v>
+        <v>-4.510180788417493</v>
       </c>
       <c r="Z2">
-        <v>8.646117273639716</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>8.646117250775207</v>
+        <v>-171.3538839821111</v>
       </c>
       <c r="AB2">
-        <v>-171.3538827377853</v>
+        <v>8.64611602550311</v>
       </c>
       <c r="AC2">
-        <v>-171.353882726353</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>-171.3538827492175</v>
+        <v>8.64611601788163</v>
       </c>
       <c r="AE2">
-        <v>8.646117262207417</v>
+        <v>-171.3538839744896</v>
       </c>
       <c r="AG2">
-        <v>0.8616798561097391</v>
+        <v>0.8999999761533819</v>
       </c>
       <c r="AH2">
-        <v>0.874328516436462</v>
+        <v>0.8070891935812007</v>
       </c>
       <c r="AI2">
-        <v>0.7641238034033052</v>
+        <v>0.7933692650240374</v>
       </c>
       <c r="AJ2">
-        <v>0.8757570807420809</v>
+        <v>0.8999999761101386</v>
       </c>
       <c r="AK2">
-        <v>0.842470205050623</v>
+        <v>0.7526371241334529</v>
       </c>
       <c r="AL2">
-        <v>0.7234729785820141</v>
+        <v>0.7897196115541287</v>
       </c>
       <c r="AM2">
-        <v>153.6843148789623</v>
+        <v>-6.662766222674398E-09</v>
       </c>
       <c r="AN2">
-        <v>25.90646318737687</v>
+        <v>-124.9369013014279</v>
       </c>
       <c r="AO2">
-        <v>-91.05627433392327</v>
+        <v>123.4923064630833</v>
       </c>
       <c r="AP2">
-        <v>155.6364982922236</v>
+        <v>-8.289607764298747E-09</v>
       </c>
       <c r="AQ2">
-        <v>25.39291890536854</v>
+        <v>-123.7575560332534</v>
       </c>
       <c r="AR2">
-        <v>-87.09305259910923</v>
+        <v>127.5936879018894</v>
       </c>
     </row>
   </sheetData>
@@ -6829,130 +6829,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0003100434204643521</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0003100440673676746</v>
+        <v>0.0005370117037640796</v>
       </c>
       <c r="D2">
-        <v>0.0006200874878316725</v>
+        <v>0.0005370113302742663</v>
       </c>
       <c r="E2">
-        <v>0.0003100434204643521</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.0003100440673676746</v>
+        <v>0.0005370117037640796</v>
       </c>
       <c r="G2">
-        <v>0.0006200874878316725</v>
+        <v>0.0005370113302742665</v>
       </c>
       <c r="H2">
-        <v>0.00358007304531132</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.003580080515107468</v>
+        <v>0.006200877034523418</v>
       </c>
       <c r="J2">
-        <v>0.007160153560414699</v>
+        <v>0.006200872721834534</v>
       </c>
       <c r="K2">
-        <v>0.00358007304531132</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>0.003580080515107468</v>
+        <v>0.006200877034523418</v>
       </c>
       <c r="M2">
-        <v>0.007160153560414699</v>
+        <v>0.006200872721834536</v>
       </c>
       <c r="N2">
-        <v>-0.0008820218792561912</v>
+        <v>5.791031014575475E-09</v>
       </c>
       <c r="O2">
-        <v>0.003285646603531229</v>
+        <v>0.005689259745651237</v>
       </c>
       <c r="P2">
-        <v>0.004807232075456474</v>
+        <v>0.001521591263049461</v>
       </c>
       <c r="Q2">
-        <v>0.000882117852377668</v>
+        <v>-5.791031014297227E-09</v>
       </c>
       <c r="R2">
-        <v>-0.003285550630009256</v>
+        <v>-0.005688971825485829</v>
       </c>
       <c r="S2">
-        <v>-0.004806848182169577</v>
+        <v>-0.001521303343284546</v>
       </c>
       <c r="T2">
-        <v>0.003284479227151636</v>
+        <v>1.053545858696311E-14</v>
       </c>
       <c r="U2">
-        <v>-0.0008787392693619498</v>
+        <v>0.00152700068824718</v>
       </c>
       <c r="V2">
-        <v>0.004811479915548996</v>
+        <v>0.005690219184760106</v>
       </c>
       <c r="W2">
-        <v>-0.003284422512266975</v>
+        <v>-1.053529415818032E-14</v>
       </c>
       <c r="X2">
-        <v>0.0008787959844832834</v>
+        <v>-0.001526830543119861</v>
       </c>
       <c r="Y2">
-        <v>-0.004811253055537008</v>
+        <v>-0.00569004903986946</v>
       </c>
       <c r="Z2">
-        <v>44.96948937997095</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>44.96936995995172</v>
+        <v>-135.0305902321537</v>
       </c>
       <c r="AB2">
-        <v>-135.0305703300988</v>
+        <v>44.96944957451684</v>
       </c>
       <c r="AC2">
-        <v>-135.0305106200217</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>-135.030630040041</v>
+        <v>44.96940976783903</v>
       </c>
       <c r="AE2">
-        <v>44.96942966989396</v>
+        <v>-135.0305504254759</v>
       </c>
       <c r="AG2">
-        <v>0.9499381296490157</v>
+        <v>0.9499999880737988</v>
       </c>
       <c r="AH2">
-        <v>0.9500137571638065</v>
+        <v>0.9499656694226498</v>
       </c>
       <c r="AI2">
-        <v>0.9499038087630082</v>
+        <v>0.949890038079251</v>
       </c>
       <c r="AJ2">
-        <v>0.9499297830099233</v>
+        <v>0.9499999880281532</v>
       </c>
       <c r="AK2">
-        <v>0.9499919530017807</v>
+        <v>0.9499137117015314</v>
       </c>
       <c r="AL2">
-        <v>0.9498435003064243</v>
+        <v>0.9498515365885972</v>
       </c>
       <c r="AM2">
-        <v>150.0011952835041</v>
+        <v>-6.66286382032093E-09</v>
       </c>
       <c r="AN2">
-        <v>29.99617149462365</v>
+        <v>-120.0064621361707</v>
       </c>
       <c r="AO2">
-        <v>-90.00526722363963</v>
+        <v>119.9985616973543</v>
       </c>
       <c r="AP2">
-        <v>150.003004693137</v>
+        <v>-8.289697842978963E-09</v>
       </c>
       <c r="AQ2">
-        <v>29.99483075058162</v>
+        <v>-120.0073345898262</v>
       </c>
       <c r="AR2">
-        <v>-90.00433015760073</v>
+        <v>120.0008398843188</v>
       </c>
     </row>
   </sheetData>
@@ -7104,130 +7104,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0002937253416077733</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.0002937259544635439</v>
+        <v>0.0005087479227884873</v>
       </c>
       <c r="D2">
-        <v>0.0005874512960709818</v>
+        <v>0.0005087475689560377</v>
       </c>
       <c r="E2">
-        <v>0.0002937253416077733</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.0002937259544635441</v>
+        <v>0.0005087479227884873</v>
       </c>
       <c r="G2">
-        <v>0.0005874512960709819</v>
+        <v>0.0005087475689560375</v>
       </c>
       <c r="H2">
-        <v>0.003391648100901254</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.003391655177550137</v>
+        <v>0.005874515003431923</v>
       </c>
       <c r="J2">
-        <v>0.006783303278447518</v>
+        <v>0.005874510917726721</v>
       </c>
       <c r="K2">
-        <v>0.003391648100901254</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>0.003391655177550139</v>
+        <v>0.005874515003431923</v>
       </c>
       <c r="M2">
-        <v>0.006783303278447519</v>
+        <v>0.00587451091772672</v>
       </c>
       <c r="N2">
-        <v>-0.0007916207227426785</v>
+        <v>5.197490295766888E-09</v>
       </c>
       <c r="O2">
-        <v>0.002948890498224175</v>
+        <v>0.005106149878641619</v>
       </c>
       <c r="P2">
-        <v>0.004314523958491612</v>
+        <v>0.001365638657841379</v>
       </c>
       <c r="Q2">
-        <v>0.0007917068592814356</v>
+        <v>-5.197490295647264E-09</v>
       </c>
       <c r="R2">
-        <v>-0.002948804361325971</v>
+        <v>-0.005105891468306464</v>
       </c>
       <c r="S2">
-        <v>-0.004314179411617689</v>
+        <v>-0.001365380247865668</v>
       </c>
       <c r="T2">
-        <v>0.002947842769868384</v>
+        <v>9.456413840569372E-15</v>
       </c>
       <c r="U2">
-        <v>-0.0007886745577119937</v>
+        <v>0.001370493654282345</v>
       </c>
       <c r="V2">
-        <v>0.004318336424285515</v>
+        <v>0.005107010981862133</v>
       </c>
       <c r="W2">
-        <v>-0.002947791867868057</v>
+        <v>-9.455745847573217E-15</v>
       </c>
       <c r="X2">
-        <v>0.000788725459924737</v>
+        <v>-0.001370340947856542</v>
       </c>
       <c r="Y2">
-        <v>-0.004318132815859383</v>
+        <v>-0.005106858275648744</v>
       </c>
       <c r="Z2">
-        <v>44.96948937997092</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>44.96936995995171</v>
+        <v>-135.0305902321537</v>
       </c>
       <c r="AB2">
-        <v>-135.0305703300988</v>
+        <v>44.96944957451681</v>
       </c>
       <c r="AC2">
-        <v>-135.0305106200218</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>-135.030630040041</v>
+        <v>44.96940976783904</v>
       </c>
       <c r="AE2">
-        <v>44.96942966989393</v>
+        <v>-135.0305504254759</v>
       </c>
       <c r="AG2">
-        <v>0.8999413734357489</v>
+        <v>0.8999999761531473</v>
       </c>
       <c r="AH2">
-        <v>0.9000130205540255</v>
+        <v>0.899967463747249</v>
       </c>
       <c r="AI2">
-        <v>0.899908858912616</v>
+        <v>0.89989581300187</v>
       </c>
       <c r="AJ2">
-        <v>0.8999334660935611</v>
+        <v>0.8999999761099042</v>
       </c>
       <c r="AK2">
-        <v>0.8999923639797626</v>
+        <v>0.8999182406437177</v>
       </c>
       <c r="AL2">
-        <v>0.8998517245861225</v>
+        <v>0.8998593379059697</v>
       </c>
       <c r="AM2">
-        <v>150.001195283504</v>
+        <v>-6.662863820381311E-09</v>
       </c>
       <c r="AN2">
-        <v>29.99617149462365</v>
+        <v>-120.0064621361707</v>
       </c>
       <c r="AO2">
-        <v>-90.00526722363963</v>
+        <v>119.9985616973543</v>
       </c>
       <c r="AP2">
-        <v>150.003004693137</v>
+        <v>-8.289697842563015E-09</v>
       </c>
       <c r="AQ2">
-        <v>29.99483075058162</v>
+        <v>-120.0073345898262</v>
       </c>
       <c r="AR2">
-        <v>-90.00433015760073</v>
+        <v>120.0008398843188</v>
       </c>
     </row>
   </sheetData>
@@ -7298,10 +7298,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0007180141641402966</v>
+        <v>0.0007180141641402969</v>
       </c>
       <c r="C2">
-        <v>0.0007180141641402966</v>
+        <v>0.0007180141641402969</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7310,40 +7310,40 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.02487274025690186</v>
+        <v>0.02487274025690187</v>
       </c>
       <c r="G2">
-        <v>0.02487274025690186</v>
+        <v>0.02487274025690187</v>
       </c>
       <c r="H2">
-        <v>0.01933569088618534</v>
+        <v>0.01933569088618537</v>
       </c>
       <c r="I2">
-        <v>-0.01933488663699849</v>
+        <v>-0.01933488663699852</v>
       </c>
       <c r="J2">
-        <v>0.0193534704897618</v>
+        <v>0.01935347048976182</v>
       </c>
       <c r="K2">
-        <v>-0.01935255797627464</v>
+        <v>-0.01935255797627465</v>
       </c>
       <c r="L2">
-        <v>104.9686321519235</v>
+        <v>-45.03136784807035</v>
       </c>
       <c r="M2">
-        <v>-75.03136784806917</v>
+        <v>134.9686321519223</v>
       </c>
       <c r="N2">
-        <v>1.099893738025532</v>
+        <v>1.099893738025533</v>
       </c>
       <c r="O2">
-        <v>1.099844930798714</v>
+        <v>1.099844930798715</v>
       </c>
       <c r="P2">
-        <v>149.9949624247528</v>
+        <v>-0.005037575241080466</v>
       </c>
       <c r="Q2">
-        <v>149.9948032546806</v>
+        <v>-0.005196745313343396</v>
       </c>
     </row>
   </sheetData>
@@ -7414,10 +7414,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.6889105335360737</v>
+        <v>0.6889105335368642</v>
       </c>
       <c r="C2">
-        <v>0.6889105335360737</v>
+        <v>0.6889105335368642</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7426,40 +7426,40 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>23.86456091907725</v>
+        <v>23.86456091910463</v>
       </c>
       <c r="G2">
-        <v>23.86456091907725</v>
+        <v>23.86456091910463</v>
       </c>
       <c r="H2">
-        <v>3.243970258588257</v>
+        <v>3.243970258585425</v>
       </c>
       <c r="I2">
-        <v>-1.822455128679596</v>
+        <v>-1.822455128673487</v>
       </c>
       <c r="J2">
-        <v>18.973238435409</v>
+        <v>18.97323843541325</v>
       </c>
       <c r="K2">
-        <v>-18.13320046022309</v>
+        <v>-18.13320046022537</v>
       </c>
       <c r="L2">
-        <v>68.6461175324325</v>
+        <v>-81.35388246757608</v>
       </c>
       <c r="M2">
-        <v>-111.3538824675602</v>
+        <v>98.64611753241661</v>
       </c>
       <c r="N2">
-        <v>0.8065751372452601</v>
+        <v>0.80657513724449</v>
       </c>
       <c r="O2">
-        <v>0.7636659323891967</v>
+        <v>0.7636659323883898</v>
       </c>
       <c r="P2">
-        <v>148.9437256189348</v>
+        <v>-1.056274381063369</v>
       </c>
       <c r="Q2">
-        <v>152.9069473327529</v>
+        <v>2.906947332764131</v>
       </c>
     </row>
   </sheetData>
@@ -7530,10 +7530,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.6526520753029245</v>
+        <v>0.6526520753036733</v>
       </c>
       <c r="C2">
-        <v>0.6526520753029245</v>
+        <v>0.6526520753036733</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7542,40 +7542,40 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>22.60853108179868</v>
+        <v>22.60853108182462</v>
       </c>
       <c r="G2">
-        <v>22.60853108179868</v>
+        <v>22.60853108182462</v>
       </c>
       <c r="H2">
-        <v>2.911485691063559</v>
+        <v>2.911485691061011</v>
       </c>
       <c r="I2">
-        <v>-1.635666053259437</v>
+        <v>-1.635666053253948</v>
       </c>
       <c r="J2">
-        <v>17.02861241455103</v>
+        <v>17.02861241455484</v>
       </c>
       <c r="K2">
-        <v>-16.27467253540795</v>
+        <v>-16.27467253541</v>
       </c>
       <c r="L2">
-        <v>68.64611753243253</v>
+        <v>-81.35388246757608</v>
       </c>
       <c r="M2">
-        <v>-111.3538824675602</v>
+        <v>98.64611753241662</v>
       </c>
       <c r="N2">
-        <v>0.7641238035784736</v>
+        <v>0.764123803577744</v>
       </c>
       <c r="O2">
-        <v>0.7234729784921393</v>
+        <v>0.7234729784913748</v>
       </c>
       <c r="P2">
-        <v>148.9437256189348</v>
+        <v>-1.05627438106337</v>
       </c>
       <c r="Q2">
-        <v>152.9069473327529</v>
+        <v>2.90694733276413</v>
       </c>
     </row>
   </sheetData>
@@ -7646,10 +7646,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0006200874878169702</v>
+        <v>0.00062008748781697</v>
       </c>
       <c r="C2">
-        <v>0.0006200874878169702</v>
+        <v>0.00062008748781697</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7658,10 +7658,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.02148046068073479</v>
+        <v>0.02148046068073478</v>
       </c>
       <c r="G2">
-        <v>0.02148046068073479</v>
+        <v>0.02148046068073478</v>
       </c>
       <c r="H2">
         <v>0.01442169622637078</v>
@@ -7670,28 +7670,28 @@
         <v>-0.01442054454651014</v>
       </c>
       <c r="J2">
-        <v>0.01443443974596181</v>
+        <v>0.01443443974596179</v>
       </c>
       <c r="K2">
-        <v>-0.01443375916592587</v>
+        <v>-0.01443375916592586</v>
       </c>
       <c r="L2">
-        <v>104.969429671254</v>
+        <v>-45.03057032873991</v>
       </c>
       <c r="M2">
-        <v>-75.0305703287387</v>
+        <v>134.9694296712528</v>
       </c>
       <c r="N2">
-        <v>0.9499038087630102</v>
+        <v>0.9499038087630096</v>
       </c>
       <c r="O2">
-        <v>0.9498435003064272</v>
+        <v>0.9498435003064266</v>
       </c>
       <c r="P2">
-        <v>149.9947327763505</v>
+        <v>-0.005267223643389584</v>
       </c>
       <c r="Q2">
-        <v>149.9956698423893</v>
+        <v>-0.004330157604604892</v>
       </c>
     </row>
   </sheetData>
@@ -7762,10 +7762,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0005874512960570527</v>
+        <v>0.0005874512960570529</v>
       </c>
       <c r="C2">
-        <v>0.0005874512960570527</v>
+        <v>0.0005874512960570529</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7774,10 +7774,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.02034990983486003</v>
+        <v>0.02034990983486004</v>
       </c>
       <c r="G2">
-        <v>0.02034990983486003</v>
+        <v>0.02034990983486004</v>
       </c>
       <c r="H2">
         <v>0.01294357187547605</v>
@@ -7792,22 +7792,22 @@
         <v>-0.0129543984469632</v>
       </c>
       <c r="L2">
-        <v>104.969429671254</v>
+        <v>-45.03057032873992</v>
       </c>
       <c r="M2">
-        <v>-75.0305703287387</v>
+        <v>134.9694296712528</v>
       </c>
       <c r="N2">
-        <v>0.8999088589126178</v>
+        <v>0.8999088589126175</v>
       </c>
       <c r="O2">
-        <v>0.8998517245861254</v>
+        <v>0.8998517245861249</v>
       </c>
       <c r="P2">
-        <v>149.9947327763505</v>
+        <v>-0.005267223643389584</v>
       </c>
       <c r="Q2">
-        <v>149.9956698423893</v>
+        <v>-0.004330157604604892</v>
       </c>
     </row>
   </sheetData>
@@ -7956,130 +7956,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.4005035588965678</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4005035588965685</v>
+        <v>0.6936925147039834</v>
       </c>
       <c r="D2">
-        <v>0.8010071177931363</v>
+        <v>0.6936925147039822</v>
       </c>
       <c r="E2">
-        <v>0.4005035588965677</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.4005035588965685</v>
+        <v>0.693692514703983</v>
       </c>
       <c r="G2">
-        <v>0.8010071177931362</v>
+        <v>0.6936925147039822</v>
       </c>
       <c r="H2">
-        <v>4.624616750806732</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>4.624616750806739</v>
+        <v>8.010071201983466</v>
       </c>
       <c r="J2">
-        <v>9.249233501613469</v>
+        <v>8.01007120198345</v>
       </c>
       <c r="K2">
-        <v>4.62461675080673</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>4.624616750806739</v>
+        <v>8.010071201983461</v>
       </c>
       <c r="M2">
-        <v>9.249233501613469</v>
+        <v>8.01007120198345</v>
       </c>
       <c r="N2">
-        <v>-3.89500766463348</v>
+        <v>7.460698386657905E-15</v>
       </c>
       <c r="O2">
-        <v>4.452761506686629</v>
+        <v>5.010515199559119</v>
       </c>
       <c r="P2">
-        <v>1.115507684106296</v>
+        <v>-3.337254021897312</v>
       </c>
       <c r="Q2">
-        <v>3.978417278712606</v>
+        <v>-8.704148117767553E-15</v>
       </c>
       <c r="R2">
-        <v>-4.369351892607506</v>
+        <v>-4.760286355819007</v>
       </c>
       <c r="S2">
-        <v>-0.7818692277897932</v>
+        <v>3.587482865637428</v>
       </c>
       <c r="T2">
-        <v>2.552472419711091</v>
+        <v>-4.973798924438583E-15</v>
       </c>
       <c r="U2">
-        <v>1.526552909728714</v>
+        <v>5.605578376339597</v>
       </c>
       <c r="V2">
-        <v>8.158050658879672</v>
+        <v>6.631497685476294</v>
       </c>
       <c r="W2">
-        <v>-2.457834589731042</v>
+        <v>4.973798924438582E-15</v>
       </c>
       <c r="X2">
-        <v>-1.431915079748665</v>
+        <v>-5.321664884694417</v>
       </c>
       <c r="Y2">
-        <v>-7.77949933895948</v>
+        <v>-6.347584193831117</v>
       </c>
       <c r="Z2">
-        <v>7.006371684726333</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>7.006371684726344</v>
+        <v>-172.9936297148662</v>
       </c>
       <c r="AB2">
-        <v>-172.9936283152664</v>
+        <v>7.006370285126532</v>
       </c>
       <c r="AC2">
-        <v>-172.9936283152664</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>-172.9936283152664</v>
+        <v>7.006370285126544</v>
       </c>
       <c r="AE2">
-        <v>7.006371684726337</v>
+        <v>-172.9936297148662</v>
       </c>
       <c r="AF2">
-        <v>1.006968727000368</v>
+        <v>1.04999995231488</v>
       </c>
       <c r="AG2">
-        <v>1.017850816891722</v>
+        <v>0.9386302699734828</v>
       </c>
       <c r="AH2">
-        <v>0.890231939232939</v>
+        <v>0.9268184948822057</v>
       </c>
       <c r="AI2">
-        <v>1.011198183551657</v>
+        <v>1.04999995231488</v>
       </c>
       <c r="AJ2">
-        <v>0.9942448498972601</v>
+        <v>0.8913852170274821</v>
       </c>
       <c r="AK2">
-        <v>0.8453339436893877</v>
+        <v>0.9102563151169288</v>
       </c>
       <c r="AL2">
-        <v>153.7687857789489</v>
+        <v>1.061690060876771E-13</v>
       </c>
       <c r="AM2">
-        <v>25.92977052790803</v>
+        <v>-124.7853904642534</v>
       </c>
       <c r="AN2">
-        <v>-90.77979706265184</v>
+        <v>123.7198714302923</v>
       </c>
       <c r="AO2">
-        <v>155.2989288026441</v>
+        <v>1.035931163680483E-13</v>
       </c>
       <c r="AP2">
-        <v>25.15127078019076</v>
+        <v>-124.8066037189149</v>
       </c>
       <c r="AQ2">
-        <v>-88.73279971011979</v>
+        <v>126.4803293362903</v>
       </c>
     </row>
   </sheetData>
